--- a/scripts/ffn_discrete/performance.xlsx
+++ b/scripts/ffn_discrete/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="472">
   <si>
     <t>Model</t>
   </si>
@@ -149,7 +154,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0005129230206412214), np.float64(6.08124067681155e-69)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007528743914757941), np.float64(0.6464544358375143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9626505282308739), np.float64(0.3360077582013798)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0031280378129662726), np.float64(0.04573241552361579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0036552208012682126), np.float64(0.07984467352685155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0016287750422474198), np.float64(0.17244870573355645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002231140965970304), np.float64(0.3489119446172013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019423710300891914), np.float64(0.1208562106629558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005648579369943358), np.float64(0.001303503559505976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013894276745293579), np.float64(0.0015350967868464828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02733993478059849), np.float64(0.0018152949027422465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06855808243703752), np.float64(0.002192087528246545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13224929833066426), np.float64(0.0012033400299710157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-9.570289344356972e-05), np.float64(0.8169439333929521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00038318166498985557), np.float64(0.4834869540869568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009549977216367755), np.float64(0.14171454843553855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0026417528852584206), np.float64(0.042223952498656306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006001559093945431), np.float64(0.02063220198952611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012289396296206425), np.float64(0.017156496665623026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03026959248047268), np.float64(0.019226989806537396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05952863342287969), np.float64(0.01890439844712829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.14866379136216146), np.float64(0.0212210780719419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.28788598329556436), np.float64(0.01572670752643342)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003161959620342011), np.float64(0.0029399850345352523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001704942397179135), np.float64(0.015430291206819362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1497495800569091e-05), np.float64(0.8921691486281712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00040818217218420395), np.float64(0.0005990116955605475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010922939618896888), np.float64(1.6260457990847442e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002315259044850423), np.float64(6.15521101201251e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00524398896880838), np.float64(1.1811110853433926e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009949634729892914), np.float64(4.1145827780049717e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.023984395825873767), np.float64(8.33582869815052e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04610088090419754), np.float64(1.4475894736055565e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.874236307383925e-05), np.float64(0.7301717014364728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015919750468917473), np.float64(0.281701700410511)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002620814245198132), np.float64(0.1298710421488571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008651060044193001), np.float64(0.011559862282167722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018315635902509647), np.float64(0.006780896743544633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003410793757684266), np.float64(0.011612289185779697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007843390997077692), np.float64(0.020216752288264653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015125347461783656), np.float64(0.02514840354798357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03649490863704351), np.float64(0.027395553237040727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0757973931633421), np.float64(0.040422979463394904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-4.774312815855419e-05), np.float64(0.41538740775898436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.345959705089065e-05), np.float64(0.605867936455061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.711608214364484e-05), np.float64(0.22237171733471503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00048106269173403326), np.float64(2.470491722824834e-14)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007065854517478228), np.float64(3.4599968390237397e-16)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010306543234522535), np.float64(2.1882761578686562e-10)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017405937721178843), np.float64(9.283250050951113e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00278788173510359), np.float64(0.00028862129864079674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005828557869836482), np.float64(0.003501959107194531)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010548000126873187), np.float64(0.004923281312403035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002689765485044847), np.float64(4.7012651643907005e-43)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00032403074991785064), np.float64(1.456283754658191e-48)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00036727363553170587), np.float64(2.3841516304881504e-53)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005129234671317104), np.float64(6.079229470459368e-69)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006544031687678102), np.float64(1.161243898970366e-74)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007621362402679905), np.float64(1.8817431056227803e-73)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009082946788957836), np.float64(3.499039655276292e-62)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010175553634420899), np.float64(4.631901005514404e-43)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011898538224954435), np.float64(6.461585166646775e-25)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013779719002994615), np.float64(2.448375068433815e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2238186772700345), np.float64(0.02180232060200593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3151811591388079), np.float64(0.014981139517799317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1978358291896733), np.float64(0.007689704866908513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4074321498815831), np.float64(0.005764628190004479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04007391069479549), np.float64(0.6033695442360235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09262550209125985), np.float64(0.39173278247746074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.21128433930878038), np.float64(0.43147321411723233)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5435973135910546), np.float64(0.30461724083393105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.162200861374175), np.float64(0.3789265361792634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.839008723512081), np.float64(0.4344624259285874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001041720516305831), np.float64(0.9677513153817785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0009127504727936275), np.float64(0.9786109001593027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0023807084733170874), np.float64(0.9530689575121257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00044187893711598815), np.float64(0.9956152591922398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004744582690099063), np.float64(0.976325601777078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03537024006007313), np.float64(0.911653851010922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15949364211314462), np.float64(0.8406140100751074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23920329212706856), np.float64(0.8756046590124361)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4012787605607149), np.float64(0.7154401520433479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0128850617250698), np.float64(0.7682403950048579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00522986157414275), np.float64(0.42819444266582607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019460195221380067), np.float64(0.6562909021242639)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00013609945595642253), np.float64(0.9794431964427667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010022806751646622), np.float64(0.8914502628395107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.011498768450343937), np.float64(0.41017629137456885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.017724358913960684), np.float64(0.46793898988468885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.039117599784940386), np.float64(0.5159719171160986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0973441904734148), np.float64(0.4087670321782573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.20492957846809923), np.float64(0.4733429936294126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4043886781628463), np.float64(0.46116504561968436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0023219658686550577), np.float64(0.7396357064019834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0024375235090206473), np.float64(0.7909561484266765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0059634542662095275), np.float64(0.5792918948717258)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007445101962044058), np.float64(0.7252779696620443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.023817373112718133), np.float64(0.567749951470412)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04791078124053263), np.float64(0.5656758919365338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.11694307460733493), np.float64(0.5712571817567254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2576463187716006), np.float64(0.5285547455402588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6523179914942586), np.float64(0.5023423699626259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8871458406640791), np.float64(0.6745908920090764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008597064864762558), np.float64(0.018576380385496805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004802540629048487), np.float64(0.2337722019156339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005874919621218688), np.float64(0.23513009604087204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003704971874006931), np.float64(0.3341272077565482)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003131094009186375), np.float64(0.5506754134486793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006746112136772566), np.float64(0.49373229299524296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015582204884495758), np.float64(0.5125219800511415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.02839331701983443), np.float64(0.5389671349793593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.07152510449863898), np.float64(0.5376624113441256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.14732542526893982), np.float64(0.4863678925997865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007766096691690805), np.float64(0.49739012579625047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006161503332715436), np.float64(0.6313857383007231)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005250123359857393), np.float64(0.7026083667005016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007528526556992441), np.float64(0.6464630654735669)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011327829091873946), np.float64(0.5677145600913261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008203734340227828), np.float64(0.7229387679030735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-5.11617719556411e-05), np.float64(0.9865158502820591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004478400847898753), np.float64(0.9144446488018407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00225847511897405), np.float64(0.7284283822548759)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004669136166851993), np.float64(0.5926713904313271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.4735218528875786), np.float64(0.013581159215579862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.098376593820717), np.float64(0.03617839880928176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9897963031729717), np.float64(0.046946326429496484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1955020141328883), np.float64(0.23223783096002296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6891415106221394), np.float64(0.4909298820732546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.6242294077560437), np.float64(0.008846653275496873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.012281318420262), np.float64(0.0026728919460621385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.08932603202103), np.float64(0.00207404748385729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0847349621432), np.float64(0.0021059497369797513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2747936266107773), np.float64(0.0011019081850448915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7344745889221802), np.float64(0.08321107638144329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9397139042992875), np.float64(0.3476420699294264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.15159890665503234), np.float64(0.879540720993391)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1156019847800716), np.float64(0.26492056538082326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8748811717978986), np.float64(0.06116561304355158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.200618970398878), np.float64(0.028042133933113954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.28966245670251), np.float64(0.02229506473458134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3292223788697743), np.float64(0.02009023455506035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3186752639933186), np.float64(0.02065859356176394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4359914712210813), np.float64(0.015063781762110904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.497325560345477), np.float64(0.01270914427672063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2521166963851385), np.float64(0.02457966943187702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9273204801849046), np.float64(0.05428613040859554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1089860199131363), np.float64(0.2677625456296839)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.051541819973296696), np.float64(0.9589063773181172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9386078775672344), np.float64(0.0528932050559214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7549377563605555), np.float64(0.00018567830055079502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.394213349498583), np.float64(1.2582461177783708e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.675747328717751), np.float64(3.425652353109133e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.680928295875529), np.float64(3.3424060849790994e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.981685372259879), np.float64(0.04784924325505797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6181284905864846), np.float64(0.10602087852751028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3910997947978483), np.float64(0.16457387472703658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3281357746557215), np.float64(0.7428930814512659)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8048752305250445), np.float64(0.4211258427376225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6087293623629415), np.float64(0.10806185350045971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9942067266854053), np.float64(0.04646141026109035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.067884655658011), np.float64(0.038965132171859845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1128524916541243), np.float64(0.03491614549704735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9925704273121643), np.float64(0.04664082255362661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0241129636802433), np.float64(0.043283492634408886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.86410553453843), np.float64(0.06266535421561073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7599838039606996), np.float64(0.07878473720274554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1536446460865803), np.float64(0.24898325932478474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6658578756993145), np.float64(0.5056898980483014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.10908218541670311), np.float64(0.9131640899387407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.011488035248856), np.float64(0.3120823648067373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8633692226240537), np.float64(0.06276893566783373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.224223595482968), np.float64(0.026405982644119863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3667716517155237), np.float64(0.018176281834820594)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4561547852923549), np.float64(0.1457340031595852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3620291066311696), np.float64(0.1735641051749772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3246305943225978), np.float64(0.18566409776359624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9625670775094339), np.float64(0.33604962725029536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7352785765290062), np.float64(0.46238086497553654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5446697272463356), np.float64(0.5861293213552777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3053679522019553), np.float64(0.7601637094928259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.30105160287250743), np.float64(0.7634517446412745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2564544667468616), np.float64(0.797664497676389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4115274071222121), np.float64(0.6807937812525108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005081851888258743), np.float64(0.11082853288836023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007032124453941751), np.float64(0.11281008612272442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002729869795112198), np.float64(0.18175148818813908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0026273949377567853), np.float64(0.30568869836917145)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0016508358716034626), np.float64(0.1290474032526422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005090515391311982), np.float64(4.080463868254745e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012501072032158285), np.float64(5.3324044880357724e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02505623218006596), np.float64(0.000170822380144971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06335241459714806), np.float64(0.000317567912920319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12448144130700099), np.float64(0.0002868782818095495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00024741683843833805), np.float64(0.46909467397585414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001375377416333077), np.float64(0.7447648145481198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006848669217558229), np.float64(0.15082071703010952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002388811281573102), np.float64(0.032386456572152125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004691066863084777), np.float64(0.0010305841689078772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009168540320653618), np.float64(0.00047723503580482027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021175090149667015), np.float64(0.00021058359383235688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04061501188350574), np.float64(0.00014865963325291345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10188619300840385), np.float64(0.0003330345631236299)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20936167782600726), np.float64(0.0004727392093583181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003918106522431443), np.float64(3.0785590087646964e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00016062737316384357), np.float64(0.021622822250036963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-4.8523200310741826e-05), np.float64(0.47538170734062724)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00043536656458340424), np.float64(0.00019560598264726164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010683843079267803), np.float64(2.2175547271459717e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0022784966897323082), np.float64(3.173708192220211e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005185970614070046), np.float64(7.544621633255136e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009885240662651843), np.float64(3.318553034201563e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.023847869109598286), np.float64(7.543121824070919e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04580754924470803), np.float64(1.2742081784746517e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.646125552331098e-05), np.float64(0.8848327158259576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019064981595380448), np.float64(0.2068382927757911)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00023344149029873), np.float64(0.1434303022264933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008677432372554693), np.float64(0.0052384543859451725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001801807237313342), np.float64(0.006113793645107508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0032748565739535098), np.float64(0.008305629938891034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007345907942139022), np.float64(0.012984038907304506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.014704178570087153), np.float64(0.02224527940375408)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.036232247660311426), np.float64(0.02686267484992539)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07365024592470827), np.float64(0.03676042531120799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.725034044054669e-05), np.float64(0.3226719117376281)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.8382429927458e-07), np.float64(0.9933283047090177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.934119094071679e-05), np.float64(0.5500337218201393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004744907501758641), np.float64(8.725090170394697e-15)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006952829190565244), np.float64(6.632516578713335e-17)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001016512966922179), np.float64(6.700004000171273e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017101668666763806), np.float64(3.889297547508653e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0027294974027244545), np.float64(0.00016327227578009814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005693694959487769), np.float64(0.002434707959967789)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010383907788426008), np.float64(0.003942964472329894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00026305109843333894), np.float64(1.0587248218575057e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000317249017231524), np.float64(7.226673787896329e-47)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003609072578023641), np.float64(1.3107762066701762e-51)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005088499494103795), np.float64(2.6074397746586445e-68)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006490567154066546), np.float64(3.629312402807567e-74)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000757755643723676), np.float64(7.31279045417701e-73)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009013929124034966), np.float64(2.1168420653804888e-61)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001008750448004053), np.float64(2.2632185328390276e-42)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011849321639882948), np.float64(1.2201454223071376e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013720637325578583), np.float64(5.0603853821124335e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.36644611211798733), np.float64(0.06519465071600405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6238561414755094), np.float64(0.023542918740656123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.34697897723997567), np.float64(0.006423167325250488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4393063566078216), np.float64(0.0057434153762439336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017142328598839275), np.float64(0.7985654664448641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04654738130086479), np.float64(0.5420004607186919)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10876831345057607), np.float64(0.5651778383453012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3506074313286014), np.float64(0.3836549699943943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6051619111378236), np.float64(0.5610942783160373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4913677094201803), np.float64(0.4521023904204114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0025672443659140684), np.float64(0.9039821382503889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007033185421683349), np.float64(0.7888318991537889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.010570851811076653), np.float64(0.7212782276011864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01059954416701445), np.float64(0.8779427291527033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.028052323867556354), np.float64(0.7497208958371943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.060918652641582464), np.float64(0.7067593382040138)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.16378497240103881), np.float64(0.6393064619437239)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2952076897363993), np.float64(0.6470280617758946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.22661079048095994), np.float64(0.8929744812826014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3956611233685612), np.float64(0.9082840614709037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003342716041835304), np.float64(0.41149087793524813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0036570349068688296), np.float64(0.39956156963001666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0034233506142474423), np.float64(0.4181610554191974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004717965023194991), np.float64(0.5123261055668401)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.011390608832327277), np.float64(0.40975377633792026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016639480779671062), np.float64(0.48005427610185486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03901070424727853), np.float64(0.5063669228295165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.09630448875891526), np.float64(0.40675599552931924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19955487306875955), np.float64(0.48287725405643084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.36392496427769544), np.float64(0.5027289419504133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0034537188260994026), np.float64(0.6250927098089214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003914932279298182), np.float64(0.6764981028258717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006371862772217584), np.float64(0.5202199581751733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01274526132605828), np.float64(0.5072901033948086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.022922556844674827), np.float64(0.5708764649030766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04551498623893195), np.float64(0.5522040211485978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.11102050500843391), np.float64(0.539248512631799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.24917794837196036), np.float64(0.5209746130040834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.621042350572252), np.float64(0.5190736638291983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8607617949756913), np.float64(0.6701792366010172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008646712126658294), np.float64(0.04098938482528059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005620460546670423), np.float64(0.26924292239969627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00687949226093722), np.float64(0.2655442708737017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003810891871519208), np.float64(0.305048764123452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0037581879019612857), np.float64(0.4555693574568908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007281011468879014), np.float64(0.440609363427047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.017219740024092486), np.float64(0.4428570398405644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03237483305445197), np.float64(0.455411682939095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.080626694362854), np.float64(0.4605982670262243)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.16620482201721493), np.float64(0.413893788693884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008361293315065255), np.float64(0.4635345827442251)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006538934810937876), np.float64(0.6106775680178985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006021604763556636), np.float64(0.6621738725647918)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008039006208938837), np.float64(0.6234856434261004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011308938137014903), np.float64(0.5664960762836415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008527152815942503), np.float64(0.7123547640377521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00014459900839569302), np.float64(0.9618171616453071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00010882355393533656), np.float64(0.9791576733372669)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001834267838721706), np.float64(0.7787148392056119)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005356961440301578), np.float64(0.5462286368445949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8136768478141982), np.float64(0.07009425564563208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.687668851705612), np.float64(0.09185648945045803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.670120720288932), np.float64(0.09527851650254758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2533686442596816), np.float64(0.2104301371003178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5135053302373689), np.float64(0.6077367186373865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1116806647457973), np.float64(0.0019249625697662063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7683891199266384), np.float64(0.00017611662294158897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6919988087142435), np.float64(0.00023727831016182407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.602832992580661), np.float64(0.00033380231341760677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.664242574088434), np.float64(0.0002640783994337188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0774348569744125), np.float64(0.03807329941046661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4173840759978724), np.float64(0.15675190325710564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.579107549993159), np.float64(0.5626762324454572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0419794530033653), np.float64(0.29772943574096733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3450708631498713), np.float64(0.019261907160486712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0346343097000084), np.float64(0.0024846075482831916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.521360736130919), np.float64(0.0004531275226076626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6957045993012403), np.float64(0.00023390007939877244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.570205529115219), np.float64(0.0003775333583246783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.4931359142893457), np.float64(0.0005030363865255153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.683747463025819), np.float64(0.0074275321561130415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.24751595139537), np.float64(0.024873135613837805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.00791942730164), np.float64(0.04498063228639218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1048147299139217), np.float64(0.26956513390599135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019108330514644495), np.float64(0.9984758431984033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9011138555142082), np.float64(0.057638729442249806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7699345207063133), np.float64(0.00017504830620864112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.422173303497557), np.float64(1.1092252557903859e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.692444064147747), np.float64(3.1642784075467785e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.712813850015996), np.float64(2.871298484652197e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9601154907328604), np.float64(0.05032182529792821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5540254656356227), np.float64(0.12056560716597459)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4519464694738944), np.float64(0.14690038629494362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3573192357302335), np.float64(0.7209451097609548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7805715539230133), np.float64(0.43528062217483826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6373949468335227), np.float64(0.10193304854091075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.090666094742564), np.float64(0.03686649587618518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.105961556024522), np.float64(0.03551223650621508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.119442365874408), np.float64(0.034354124453793614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0301348160509702), np.float64(0.04266636053276143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.033127051472028), np.float64(0.04236249245237383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.916456148472889), np.float64(0.0556556779205118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8176015125848877), np.float64(0.06949122348335074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1687164032105257), np.float64(0.24285880495264583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6980153065317638), np.float64(0.48536623095062875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.12051914235996918), np.float64(0.904101548381265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9631253953196673), np.float64(0.33576957104482635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.86327328790469), np.float64(0.06278244182239902)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.244070220249738), np.float64(0.025094913769118862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.40248819678604), np.float64(0.016506130253825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.468676554485805), np.float64(0.1423054478597351)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3795415169603353), np.float64(0.16810531255946143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.326808512672512), np.float64(0.18494274315184409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9707794023691948), np.float64(0.3319454496016639)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7535378548500012), np.float64(0.4513438686091672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5408912965712381), np.float64(0.5887299466954665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3364141432685666), np.float64(0.7366449723680106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.27128663003100384), np.float64(0.7862391179544473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.20762142096925146), np.float64(0.8355763176986081)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.08981588875965157), np.float64(0.9284555349532195)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1506,10 +2792,6169 @@
         <v>44</v>
       </c>
       <c r="V12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0008404744572943121</v>
+      </c>
+      <c r="D2">
+        <v>-0.002875963691622019</v>
+      </c>
+      <c r="E2">
+        <v>0.04471812769770622</v>
+      </c>
+      <c r="F2">
+        <v>0.0008747464162297547</v>
+      </c>
+      <c r="G2">
+        <v>0.0009237055201083422</v>
+      </c>
+      <c r="H2">
+        <v>1.000299926685248</v>
+      </c>
+      <c r="I2">
+        <v>0.04911335408213065</v>
+      </c>
+      <c r="J2">
+        <v>-0.06431315094232559</v>
+      </c>
+      <c r="K2">
+        <v>-0.999920129776001</v>
+      </c>
+      <c r="L2">
+        <v>2.559502363204956</v>
+      </c>
+      <c r="M2">
+        <v>-3.681050062179565</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.001119204952458584</v>
+      </c>
+      <c r="D3">
+        <v>-0.003296702401712537</v>
+      </c>
+      <c r="E3">
+        <v>0.05964073911309242</v>
+      </c>
+      <c r="F3">
+        <v>0.001047019963152707</v>
+      </c>
+      <c r="G3">
+        <v>0.001026555080898106</v>
+      </c>
+      <c r="H3">
+        <v>1.000497481843034</v>
+      </c>
+      <c r="I3">
+        <v>0.04904174090717398</v>
+      </c>
+      <c r="J3">
+        <v>-0.05527601391077042</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999799728393555</v>
+      </c>
+      <c r="L3">
+        <v>3.413618326187134</v>
+      </c>
+      <c r="M3">
+        <v>-3.163797378540039</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001395832599919893</v>
+      </c>
+      <c r="D4">
+        <v>-0.001406375551596284</v>
+      </c>
+      <c r="E4">
+        <v>0.0341576486825943</v>
+      </c>
+      <c r="F4">
+        <v>0.001180142164230347</v>
+      </c>
+      <c r="G4">
+        <v>0.001159932580776513</v>
+      </c>
+      <c r="H4">
+        <v>1.000537015400638</v>
+      </c>
+      <c r="I4">
+        <v>0.04910407363674676</v>
+      </c>
+      <c r="J4">
+        <v>-0.04117307811975479</v>
+      </c>
+      <c r="K4">
+        <v>-0.9900532960891724</v>
+      </c>
+      <c r="L4">
+        <v>1.955059170722961</v>
+      </c>
+      <c r="M4">
+        <v>-2.356596708297729</v>
+      </c>
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002748021335149384</v>
+      </c>
+      <c r="D5">
+        <v>-0.001794629730284214</v>
+      </c>
+      <c r="E5">
+        <v>0.06821206957101822</v>
+      </c>
+      <c r="F5">
+        <v>0.001594409928657115</v>
+      </c>
+      <c r="G5">
+        <v>0.001502462429925799</v>
+      </c>
+      <c r="H5">
+        <v>1.000735006013183</v>
+      </c>
+      <c r="I5">
+        <v>0.04919688812170483</v>
+      </c>
+      <c r="J5">
+        <v>-0.02630956284701824</v>
+      </c>
+      <c r="K5">
+        <v>-0.9972177743911743</v>
+      </c>
+      <c r="L5">
+        <v>3.904209852218628</v>
+      </c>
+      <c r="M5">
+        <v>-1.505863428115845</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" t="s">
+        <v>174</v>
+      </c>
+      <c r="P5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.00538148625460645</v>
+      </c>
+      <c r="D6">
+        <v>0.001984308008104563</v>
+      </c>
+      <c r="E6">
+        <v>0.03568543866276741</v>
+      </c>
+      <c r="F6">
+        <v>0.002019689884036779</v>
+      </c>
+      <c r="G6">
+        <v>0.001880808151327074</v>
+      </c>
+      <c r="H6">
+        <v>1.000851267005455</v>
+      </c>
+      <c r="I6">
+        <v>0.04935258467325063</v>
+      </c>
+      <c r="J6">
+        <v>0.05560553818941116</v>
+      </c>
+      <c r="K6">
+        <v>660.3709716796875</v>
+      </c>
+      <c r="L6">
+        <v>2.04250431060791</v>
+      </c>
+      <c r="M6">
+        <v>3.182658195495605</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.01056962481095927</v>
+      </c>
+      <c r="D7">
+        <v>0.005737524945288897</v>
+      </c>
+      <c r="E7">
+        <v>0.04997594282031059</v>
+      </c>
+      <c r="F7">
+        <v>0.002472016494721174</v>
+      </c>
+      <c r="G7">
+        <v>0.002287204377353191</v>
+      </c>
+      <c r="H7">
+        <v>1.001037140042931</v>
+      </c>
+      <c r="I7">
+        <v>0.0491275565917767</v>
+      </c>
+      <c r="J7">
+        <v>0.1148057356476784</v>
+      </c>
+      <c r="K7">
+        <v>137960032</v>
+      </c>
+      <c r="L7">
+        <v>2.860440492630005</v>
+      </c>
+      <c r="M7">
+        <v>6.571061611175537</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02591756482085025</v>
+      </c>
+      <c r="D8">
+        <v>0.01407776027917862</v>
+      </c>
+      <c r="E8">
+        <v>0.1248078718781471</v>
+      </c>
+      <c r="F8">
+        <v>0.002890484873205423</v>
+      </c>
+      <c r="G8">
+        <v>0.002710552886128426</v>
+      </c>
+      <c r="H8">
+        <v>1.001510526557596</v>
+      </c>
+      <c r="I8">
+        <v>0.04984389899907907</v>
+      </c>
+      <c r="J8">
+        <v>0.1127954497933388</v>
+      </c>
+      <c r="K8">
+        <v>7.753068144602015E+19</v>
+      </c>
+      <c r="L8">
+        <v>7.143547058105469</v>
+      </c>
+      <c r="M8">
+        <v>6.455999851226807</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" t="s">
+        <v>177</v>
+      </c>
+      <c r="P8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.0513707406217497</v>
+      </c>
+      <c r="D9">
+        <v>0.02780239097774029</v>
+      </c>
+      <c r="E9">
+        <v>0.2495635598897934</v>
+      </c>
+      <c r="F9">
+        <v>0.003144754562526941</v>
+      </c>
+      <c r="G9">
+        <v>0.002998102689161897</v>
+      </c>
+      <c r="H9">
+        <v>1.001778290502006</v>
+      </c>
+      <c r="I9">
+        <v>0.0505734551564947</v>
+      </c>
+      <c r="J9">
+        <v>0.1114040464162827</v>
+      </c>
+      <c r="K9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9">
+        <v>14.28410720825195</v>
+      </c>
+      <c r="M9">
+        <v>6.376360893249512</v>
+      </c>
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1291586426260459</v>
+      </c>
+      <c r="D10">
+        <v>0.06955524533987045</v>
+      </c>
+      <c r="E10">
+        <v>0.6372359991073608</v>
+      </c>
+      <c r="F10">
+        <v>0.003467880422249436</v>
+      </c>
+      <c r="G10">
+        <v>0.003433225909247994</v>
+      </c>
+      <c r="H10">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I10">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J10">
+        <v>0.1091514676809311</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>36.47306442260742</v>
+      </c>
+      <c r="M10">
+        <v>6.247431755065918</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.2490752073417374</v>
+      </c>
+      <c r="D11">
+        <v>0.1339370757341385</v>
+      </c>
+      <c r="E11">
+        <v>1.162080407142639</v>
+      </c>
+      <c r="F11">
+        <v>0.003685290459543467</v>
+      </c>
+      <c r="G11">
+        <v>0.003709133481606841</v>
+      </c>
+      <c r="H11">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I11">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J11">
+        <v>0.1152562871575356</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>66.51324462890625</v>
+      </c>
+      <c r="M11">
+        <v>6.59684944152832</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" t="s">
+        <v>180</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001674614449769164</v>
+      </c>
+      <c r="D12">
+        <v>-9.454598330194131E-05</v>
+      </c>
+      <c r="E12">
+        <v>0.01178540755063295</v>
+      </c>
+      <c r="F12">
+        <v>0.0008993298397399485</v>
+      </c>
+      <c r="G12">
+        <v>0.0009400542476214468</v>
+      </c>
+      <c r="H12">
+        <v>1.000254108663114</v>
+      </c>
+      <c r="I12">
+        <v>0.04913507572204717</v>
+      </c>
+      <c r="J12">
+        <v>-0.008022292517125607</v>
+      </c>
+      <c r="K12">
+        <v>-0.2663363814353943</v>
+      </c>
+      <c r="L12">
+        <v>0.6745537519454956</v>
+      </c>
+      <c r="M12">
+        <v>-0.4591667652130127</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.002230702728985471</v>
+      </c>
+      <c r="D13">
+        <v>0.0003821619611699134</v>
+      </c>
+      <c r="E13">
+        <v>0.01558578200638294</v>
+      </c>
+      <c r="F13">
+        <v>0.001080363988876343</v>
+      </c>
+      <c r="G13">
+        <v>0.001049546292051673</v>
+      </c>
+      <c r="H13">
+        <v>1.00039950903539</v>
+      </c>
+      <c r="I13">
+        <v>0.04912488362534282</v>
+      </c>
+      <c r="J13">
+        <v>0.0245199091732502</v>
+      </c>
+      <c r="K13">
+        <v>2.49662709236145</v>
+      </c>
+      <c r="L13">
+        <v>0.8920732736587524</v>
+      </c>
+      <c r="M13">
+        <v>1.403430104255676</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002783679079980188</v>
+      </c>
+      <c r="D14">
+        <v>0.0009524209890514612</v>
+      </c>
+      <c r="E14">
+        <v>0.01851627416908741</v>
+      </c>
+      <c r="F14">
+        <v>0.001229496905580163</v>
+      </c>
+      <c r="G14">
+        <v>0.001170900301076472</v>
+      </c>
+      <c r="H14">
+        <v>1.000447788663984</v>
+      </c>
+      <c r="I14">
+        <v>0.04917306857636058</v>
+      </c>
+      <c r="J14">
+        <v>0.05143696814775467</v>
+      </c>
+      <c r="K14">
+        <v>21.61145210266113</v>
+      </c>
+      <c r="L14">
+        <v>1.05980396270752</v>
+      </c>
+      <c r="M14">
+        <v>2.944064378738403</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.005519729531120734</v>
+      </c>
+      <c r="D15">
+        <v>0.002641282044351101</v>
+      </c>
+      <c r="E15">
+        <v>0.03703377395868301</v>
+      </c>
+      <c r="F15">
+        <v>0.00162509735673666</v>
+      </c>
+      <c r="G15">
+        <v>0.001525479601696134</v>
+      </c>
+      <c r="H15">
+        <v>1.000604795432144</v>
+      </c>
+      <c r="I15">
+        <v>0.04926832126765576</v>
+      </c>
+      <c r="J15">
+        <v>0.07132089883089066</v>
+      </c>
+      <c r="K15">
+        <v>5661.14208984375</v>
+      </c>
+      <c r="L15">
+        <v>2.119678020477295</v>
+      </c>
+      <c r="M15">
+        <v>4.08214807510376</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.01091316798608192</v>
+      </c>
+      <c r="D16">
+        <v>0.006006561685353518</v>
+      </c>
+      <c r="E16">
+        <v>0.07381091266870499</v>
+      </c>
+      <c r="F16">
+        <v>0.002080907113850117</v>
+      </c>
+      <c r="G16">
+        <v>0.001933487830683589</v>
+      </c>
+      <c r="H16">
+        <v>1.000780940408391</v>
+      </c>
+      <c r="I16">
+        <v>0.04940230163263215</v>
+      </c>
+      <c r="J16">
+        <v>0.08137769252061844</v>
+      </c>
+      <c r="K16">
+        <v>331372736</v>
+      </c>
+      <c r="L16">
+        <v>4.224667072296143</v>
+      </c>
+      <c r="M16">
+        <v>4.657762050628662</v>
+      </c>
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" t="s">
+        <v>185</v>
+      </c>
+      <c r="P16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.02157238238367861</v>
+      </c>
+      <c r="D17">
+        <v>0.01232346799224615</v>
+      </c>
+      <c r="E17">
+        <v>0.14682337641716</v>
+      </c>
+      <c r="F17">
+        <v>0.002523394301533699</v>
+      </c>
+      <c r="G17">
+        <v>0.00232853926718235</v>
+      </c>
+      <c r="H17">
+        <v>1.001010218249182</v>
+      </c>
+      <c r="I17">
+        <v>0.04914224366446068</v>
+      </c>
+      <c r="J17">
+        <v>0.08393396437168121</v>
+      </c>
+      <c r="K17">
+        <v>2.667387377596498E+17</v>
+      </c>
+      <c r="L17">
+        <v>8.403634071350098</v>
+      </c>
+      <c r="M17">
+        <v>4.804073810577393</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O17" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.05349210523834295</v>
+      </c>
+      <c r="D18">
+        <v>0.0304153747856617</v>
+      </c>
+      <c r="E18">
+        <v>0.3682637810707092</v>
+      </c>
+      <c r="F18">
+        <v>0.002935906872153282</v>
+      </c>
+      <c r="G18">
+        <v>0.002766142599284649</v>
+      </c>
+      <c r="H18">
+        <v>1.001499103478249</v>
+      </c>
+      <c r="I18">
+        <v>0.04983330815167534</v>
+      </c>
+      <c r="J18">
+        <v>0.08259127289056778</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18">
+        <v>21.07807540893555</v>
+      </c>
+      <c r="M18">
+        <v>4.727222919464111</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" t="s">
+        <v>187</v>
+      </c>
+      <c r="P18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.1053544284477314</v>
+      </c>
+      <c r="D19">
+        <v>0.05974749475717545</v>
+      </c>
+      <c r="E19">
+        <v>0.7223102450370789</v>
+      </c>
+      <c r="F19">
+        <v>0.003161109983921051</v>
+      </c>
+      <c r="G19">
+        <v>0.003055082634091377</v>
+      </c>
+      <c r="H19">
+        <v>1.001803345489537</v>
+      </c>
+      <c r="I19">
+        <v>0.05031258446840677</v>
+      </c>
+      <c r="J19">
+        <v>0.08271721750497818</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>41.34240341186523</v>
+      </c>
+      <c r="M19">
+        <v>4.734431743621826</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" t="s">
+        <v>188</v>
+      </c>
+      <c r="P19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.2653119178863212</v>
+      </c>
+      <c r="D20">
+        <v>0.1499074995517731</v>
+      </c>
+      <c r="E20">
+        <v>1.838288307189941</v>
+      </c>
+      <c r="F20">
+        <v>0.003487326437607408</v>
+      </c>
+      <c r="G20">
+        <v>0.003437733976170421</v>
+      </c>
+      <c r="H20">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I20">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J20">
+        <v>0.0815473273396492</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>105.216911315918</v>
+      </c>
+      <c r="M20">
+        <v>4.667471408843994</v>
+      </c>
+      <c r="N20" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.5116057494383327</v>
+      </c>
+      <c r="D21">
+        <v>0.2901052534580231</v>
+      </c>
+      <c r="E21">
+        <v>3.393283128738403</v>
+      </c>
+      <c r="F21">
+        <v>0.003676220308989286</v>
+      </c>
+      <c r="G21">
+        <v>0.003720982000231743</v>
+      </c>
+      <c r="H21">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I21">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J21">
+        <v>0.08549397438764572</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>194.2191467285156</v>
+      </c>
+      <c r="M21">
+        <v>4.893362998962402</v>
+      </c>
+      <c r="N21" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0003499051604225031</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003220022772438824</v>
+      </c>
+      <c r="E22">
+        <v>0.003023781813681126</v>
+      </c>
+      <c r="F22">
+        <v>0.000939509307499975</v>
+      </c>
+      <c r="G22">
+        <v>0.0009490713127888739</v>
+      </c>
+      <c r="H22">
+        <v>1.00014545061725</v>
+      </c>
+      <c r="I22">
+        <v>0.04922734720648508</v>
+      </c>
+      <c r="J22">
+        <v>-0.1064899191260338</v>
+      </c>
+      <c r="K22">
+        <v>-0.6518042087554932</v>
+      </c>
+      <c r="L22">
+        <v>0.1730702370405197</v>
+      </c>
+      <c r="M22">
+        <v>-6.095094203948975</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+      <c r="O22" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0004632286505819032</v>
+      </c>
+      <c r="D23">
+        <v>-0.0001726402988424525</v>
+      </c>
+      <c r="E23">
+        <v>0.002003263449296355</v>
+      </c>
+      <c r="F23">
+        <v>0.001131777884438634</v>
+      </c>
+      <c r="G23">
+        <v>0.001079217647202313</v>
+      </c>
+      <c r="H23">
+        <v>1.000300167780387</v>
+      </c>
+      <c r="I23">
+        <v>0.04921148326618179</v>
+      </c>
+      <c r="J23">
+        <v>-0.08617952466011047</v>
+      </c>
+      <c r="K23">
+        <v>-0.4319442510604858</v>
+      </c>
+      <c r="L23">
+        <v>0.1146594882011414</v>
+      </c>
+      <c r="M23">
+        <v>-4.932601451873779</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" t="s">
+        <v>192</v>
+      </c>
+      <c r="P23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0005730643979519192</v>
+      </c>
+      <c r="D24">
+        <v>-1.164462446467951E-05</v>
+      </c>
+      <c r="E24">
+        <v>0.002418025163933635</v>
+      </c>
+      <c r="F24">
+        <v>0.001284598140046</v>
+      </c>
+      <c r="G24">
+        <v>0.001209558802656829</v>
+      </c>
+      <c r="H24">
+        <v>1.000337295834847</v>
+      </c>
+      <c r="I24">
+        <v>0.0492557146088796</v>
+      </c>
+      <c r="J24">
+        <v>-0.00481575820595026</v>
+      </c>
+      <c r="K24">
+        <v>-0.0373610258102417</v>
+      </c>
+      <c r="L24">
+        <v>0.1383989304304123</v>
+      </c>
+      <c r="M24">
+        <v>-0.2756364345550537</v>
+      </c>
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+      <c r="P24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001086616410697315</v>
+      </c>
+      <c r="D25">
+        <v>0.0004092314629815519</v>
+      </c>
+      <c r="E25">
+        <v>0.003379057161509991</v>
+      </c>
+      <c r="F25">
+        <v>0.001668843789957464</v>
+      </c>
+      <c r="G25">
+        <v>0.001570416847243905</v>
+      </c>
+      <c r="H25">
+        <v>1.000478166966723</v>
+      </c>
+      <c r="I25">
+        <v>0.04933222683788786</v>
+      </c>
+      <c r="J25">
+        <v>0.1211081817746162</v>
+      </c>
+      <c r="K25">
+        <v>2.820624828338623</v>
+      </c>
+      <c r="L25">
+        <v>0.1934048980474472</v>
+      </c>
+      <c r="M25">
+        <v>6.931790351867676</v>
+      </c>
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O25" t="s">
+        <v>194</v>
+      </c>
+      <c r="P25" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.002034679847887795</v>
+      </c>
+      <c r="D26">
+        <v>0.001080237096175551</v>
+      </c>
+      <c r="E26">
+        <v>0.006452412344515324</v>
+      </c>
+      <c r="F26">
+        <v>0.002135447924956679</v>
+      </c>
+      <c r="G26">
+        <v>0.00198213686235249</v>
+      </c>
+      <c r="H26">
+        <v>1.000654249383713</v>
+      </c>
+      <c r="I26">
+        <v>0.04952526798137051</v>
+      </c>
+      <c r="J26">
+        <v>0.1674160063266754</v>
+      </c>
+      <c r="K26">
+        <v>33.36605834960938</v>
+      </c>
+      <c r="L26">
+        <v>0.3693125247955322</v>
+      </c>
+      <c r="M26">
+        <v>9.582281112670898</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
+        <v>195</v>
+      </c>
+      <c r="P26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.003830573043984939</v>
+      </c>
+      <c r="D27">
+        <v>0.00229842378757894</v>
+      </c>
+      <c r="E27">
+        <v>0.01124837435781956</v>
+      </c>
+      <c r="F27">
+        <v>0.002574574667960405</v>
+      </c>
+      <c r="G27">
+        <v>0.002396146068349481</v>
+      </c>
+      <c r="H27">
+        <v>1.001012408425398</v>
+      </c>
+      <c r="I27">
+        <v>0.0491296656307449</v>
+      </c>
+      <c r="J27">
+        <v>0.2043338567018509</v>
+      </c>
+      <c r="K27">
+        <v>1845.711059570312</v>
+      </c>
+      <c r="L27">
+        <v>0.6438158750534058</v>
+      </c>
+      <c r="M27">
+        <v>11.6953239440918</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+      <c r="O27" t="s">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.009051345727655319</v>
+      </c>
+      <c r="D28">
+        <v>0.005208298563957214</v>
+      </c>
+      <c r="E28">
+        <v>0.02801206335425377</v>
+      </c>
+      <c r="F28">
+        <v>0.00298417522571981</v>
+      </c>
+      <c r="G28">
+        <v>0.002823765622451901</v>
+      </c>
+      <c r="H28">
+        <v>1.00150069898012</v>
+      </c>
+      <c r="I28">
+        <v>0.0498556267301185</v>
+      </c>
+      <c r="J28">
+        <v>0.1859305649995804</v>
+      </c>
+      <c r="K28">
+        <v>24592720</v>
+      </c>
+      <c r="L28">
+        <v>1.603308320045471</v>
+      </c>
+      <c r="M28">
+        <v>10.64198684692383</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" t="s">
+        <v>197</v>
+      </c>
+      <c r="P28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.01755920107055843</v>
+      </c>
+      <c r="D29">
+        <v>0.009864496067166328</v>
+      </c>
+      <c r="E29">
+        <v>0.05565179884433746</v>
+      </c>
+      <c r="F29">
+        <v>0.003197799203917384</v>
+      </c>
+      <c r="G29">
+        <v>0.003092089435085654</v>
+      </c>
+      <c r="H29">
+        <v>1.001829953972321</v>
+      </c>
+      <c r="I29">
+        <v>0.05029435254934062</v>
+      </c>
+      <c r="J29">
+        <v>0.177253857254982</v>
+      </c>
+      <c r="K29">
+        <v>92440623054848</v>
+      </c>
+      <c r="L29">
+        <v>3.185305833816528</v>
+      </c>
+      <c r="M29">
+        <v>10.14536380767822</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+      <c r="O29" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.04313806065094353</v>
+      </c>
+      <c r="D30">
+        <v>0.02377858385443687</v>
+      </c>
+      <c r="E30">
+        <v>0.1378553360700607</v>
+      </c>
+      <c r="F30">
+        <v>0.003509510308504105</v>
+      </c>
+      <c r="G30">
+        <v>0.003505394561216235</v>
+      </c>
+      <c r="H30">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I30">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J30">
+        <v>0.1724894046783447</v>
+      </c>
+      <c r="K30">
+        <v>2.722401601083992E+33</v>
+      </c>
+      <c r="L30">
+        <v>7.890336513519287</v>
+      </c>
+      <c r="M30">
+        <v>9.872664451599121</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>199</v>
+      </c>
+      <c r="P30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.08358939391979031</v>
+      </c>
+      <c r="D31">
+        <v>0.04564264416694641</v>
+      </c>
+      <c r="E31">
+        <v>0.2709593772888184</v>
+      </c>
+      <c r="F31">
+        <v>0.003710360266268253</v>
+      </c>
+      <c r="G31">
+        <v>0.003818884026259184</v>
+      </c>
+      <c r="H31">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I31">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J31">
+        <v>0.1684482842683792</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>15.50872611999512</v>
+      </c>
+      <c r="M31">
+        <v>9.641365051269531</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s">
+        <v>200</v>
+      </c>
+      <c r="P31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.000507655662355613</v>
+      </c>
+      <c r="D32">
+        <v>-4.128543514525518E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003202415537089109</v>
+      </c>
+      <c r="F32">
+        <v>0.001005192403681576</v>
+      </c>
+      <c r="G32">
+        <v>0.001009042840451002</v>
+      </c>
+      <c r="H32">
+        <v>1.000022250198475</v>
+      </c>
+      <c r="I32">
+        <v>0.04935993139044631</v>
+      </c>
+      <c r="J32">
+        <v>-0.01289196684956551</v>
+      </c>
+      <c r="K32">
+        <v>-0.1265648007392883</v>
+      </c>
+      <c r="L32">
+        <v>0.1832945793867111</v>
+      </c>
+      <c r="M32">
+        <v>-0.7378891110420227</v>
+      </c>
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+      <c r="O32" t="s">
+        <v>201</v>
+      </c>
+      <c r="P32" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0006713424333867366</v>
+      </c>
+      <c r="D33">
+        <v>0.000156522510224022</v>
+      </c>
+      <c r="E33">
+        <v>0.004214521031826735</v>
+      </c>
+      <c r="F33">
+        <v>0.001204758416861296</v>
+      </c>
+      <c r="G33">
+        <v>0.001149832969531417</v>
+      </c>
+      <c r="H33">
+        <v>1.000178579472377</v>
+      </c>
+      <c r="I33">
+        <v>0.0493429633153899</v>
+      </c>
+      <c r="J33">
+        <v>0.03713886067271233</v>
+      </c>
+      <c r="K33">
+        <v>0.6698358058929443</v>
+      </c>
+      <c r="L33">
+        <v>0.2412238121032715</v>
+      </c>
+      <c r="M33">
+        <v>2.125692844390869</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+      <c r="O33" t="s">
+        <v>202</v>
+      </c>
+      <c r="P33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0008307459077743418</v>
+      </c>
+      <c r="D34">
+        <v>0.0002556599793024361</v>
+      </c>
+      <c r="E34">
+        <v>0.004930750001221895</v>
+      </c>
+      <c r="F34">
+        <v>0.001347028417512774</v>
+      </c>
+      <c r="G34">
+        <v>0.001268920954316854</v>
+      </c>
+      <c r="H34">
+        <v>1.000237542681657</v>
+      </c>
+      <c r="I34">
+        <v>0.04932830351802897</v>
+      </c>
+      <c r="J34">
+        <v>0.05185012146830559</v>
+      </c>
+      <c r="K34">
+        <v>1.310765743255615</v>
+      </c>
+      <c r="L34">
+        <v>0.2822181284427643</v>
+      </c>
+      <c r="M34">
+        <v>2.967711687088013</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+      <c r="O34" t="s">
+        <v>203</v>
+      </c>
+      <c r="P34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001589050655030727</v>
+      </c>
+      <c r="D35">
+        <v>0.0008571073412895203</v>
+      </c>
+      <c r="E35">
+        <v>0.009748829528689384</v>
+      </c>
+      <c r="F35">
+        <v>0.001705812755972147</v>
+      </c>
+      <c r="G35">
+        <v>0.001606679055839777</v>
+      </c>
+      <c r="H35">
+        <v>1.000363595982694</v>
+      </c>
+      <c r="I35">
+        <v>0.04946966089912421</v>
+      </c>
+      <c r="J35">
+        <v>0.08791899681091309</v>
+      </c>
+      <c r="K35">
+        <v>15.55528450012207</v>
+      </c>
+      <c r="L35">
+        <v>0.5579874515533447</v>
+      </c>
+      <c r="M35">
+        <v>5.032162666320801</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+      <c r="O35" t="s">
+        <v>204</v>
+      </c>
+      <c r="P35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.003023410913982391</v>
+      </c>
+      <c r="D36">
+        <v>0.001805572654120624</v>
+      </c>
+      <c r="E36">
+        <v>0.019247155636549</v>
+      </c>
+      <c r="F36">
+        <v>0.00218497053720057</v>
+      </c>
+      <c r="G36">
+        <v>0.002033860189840198</v>
+      </c>
+      <c r="H36">
+        <v>1.000549064095571</v>
+      </c>
+      <c r="I36">
+        <v>0.04968318851426422</v>
+      </c>
+      <c r="J36">
+        <v>0.09380984306335449</v>
+      </c>
+      <c r="K36">
+        <v>367.5691528320312</v>
+      </c>
+      <c r="L36">
+        <v>1.101637005805969</v>
+      </c>
+      <c r="M36">
+        <v>5.369333267211914</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" t="s">
+        <v>205</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.005782737596970712</v>
+      </c>
+      <c r="D37">
+        <v>0.003362935269251466</v>
+      </c>
+      <c r="E37">
+        <v>0.03847714141011238</v>
+      </c>
+      <c r="F37">
+        <v>0.00262275617569685</v>
+      </c>
+      <c r="G37">
+        <v>0.002447563456371427</v>
+      </c>
+      <c r="H37">
+        <v>1.000968441692069</v>
+      </c>
+      <c r="I37">
+        <v>0.04919660743831585</v>
+      </c>
+      <c r="J37">
+        <v>0.08740086108446121</v>
+      </c>
+      <c r="K37">
+        <v>59774.91796875</v>
+      </c>
+      <c r="L37">
+        <v>2.202291250228882</v>
+      </c>
+      <c r="M37">
+        <v>5.002506256103516</v>
+      </c>
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" t="s">
+        <v>206</v>
+      </c>
+      <c r="P37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01388971956847574</v>
+      </c>
+      <c r="D38">
+        <v>0.007736950647085905</v>
+      </c>
+      <c r="E38">
+        <v>0.09621752798557281</v>
+      </c>
+      <c r="F38">
+        <v>0.003028306178748608</v>
+      </c>
+      <c r="G38">
+        <v>0.002880374202504754</v>
+      </c>
+      <c r="H38">
+        <v>1.001568095096138</v>
+      </c>
+      <c r="I38">
+        <v>0.04978580473851281</v>
+      </c>
+      <c r="J38">
+        <v>0.08041103184223175</v>
+      </c>
+      <c r="K38">
+        <v>92327370752</v>
+      </c>
+      <c r="L38">
+        <v>5.507140159606934</v>
+      </c>
+      <c r="M38">
+        <v>4.602434158325195</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O38" t="s">
+        <v>207</v>
+      </c>
+      <c r="P38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02731180437220587</v>
+      </c>
+      <c r="D39">
+        <v>0.01489361561834812</v>
+      </c>
+      <c r="E39">
+        <v>0.1924856305122375</v>
+      </c>
+      <c r="F39">
+        <v>0.00323281972669065</v>
+      </c>
+      <c r="G39">
+        <v>0.003171072108671069</v>
+      </c>
+      <c r="H39">
+        <v>1.001806988317537</v>
+      </c>
+      <c r="I39">
+        <v>0.05034160335526899</v>
+      </c>
+      <c r="J39">
+        <v>0.07737521082162857</v>
+      </c>
+      <c r="K39">
+        <v>1.080624445732482E+21</v>
+      </c>
+      <c r="L39">
+        <v>11.01717472076416</v>
+      </c>
+      <c r="M39">
+        <v>4.428674697875977</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+      <c r="O39" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.06682523556559301</v>
+      </c>
+      <c r="D40">
+        <v>0.03585574775934219</v>
+      </c>
+      <c r="E40">
+        <v>0.471395343542099</v>
+      </c>
+      <c r="F40">
+        <v>0.003516997676342726</v>
+      </c>
+      <c r="G40">
+        <v>0.003553528105840087</v>
+      </c>
+      <c r="H40">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I40">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J40">
+        <v>0.07606300711631775</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>26.98094940185547</v>
+      </c>
+      <c r="M40">
+        <v>4.353569030761719</v>
+      </c>
+      <c r="N40" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1402563994148378</v>
+      </c>
+      <c r="D41">
+        <v>0.07465607672929764</v>
+      </c>
+      <c r="E41">
+        <v>1.052721619606018</v>
+      </c>
+      <c r="F41">
+        <v>0.003744930494576693</v>
+      </c>
+      <c r="G41">
+        <v>0.00381373567506671</v>
+      </c>
+      <c r="H41">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I41">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J41">
+        <v>0.07091720402240753</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>60.25394439697266</v>
+      </c>
+      <c r="M41">
+        <v>4.059041976928711</v>
+      </c>
+      <c r="N41" t="s">
+        <v>150</v>
+      </c>
+      <c r="O41" t="s">
+        <v>210</v>
+      </c>
+      <c r="P41" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001848151459745053</v>
+      </c>
+      <c r="D42">
+        <v>-3.833996379398741E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001676500425674021</v>
+      </c>
+      <c r="F42">
+        <v>0.001116575673222542</v>
+      </c>
+      <c r="G42">
+        <v>0.00107409677002579</v>
+      </c>
+      <c r="H42">
+        <v>0.9998393813150729</v>
+      </c>
+      <c r="I42">
+        <v>0.04949228483172896</v>
+      </c>
+      <c r="J42">
+        <v>-0.02286904491484165</v>
+      </c>
+      <c r="K42">
+        <v>-0.1179951429367065</v>
+      </c>
+      <c r="L42">
+        <v>0.09595676511526108</v>
+      </c>
+      <c r="M42">
+        <v>-1.308940649032593</v>
+      </c>
+      <c r="N42" t="s">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s">
+        <v>211</v>
+      </c>
+      <c r="P42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0002369010774519801</v>
+      </c>
+      <c r="D43">
+        <v>3.868039493681863E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.00185017439071089</v>
+      </c>
+      <c r="F43">
+        <v>0.001292467233724892</v>
+      </c>
+      <c r="G43">
+        <v>0.001216211821883917</v>
+      </c>
+      <c r="H43">
+        <v>0.9999577536519116</v>
+      </c>
+      <c r="I43">
+        <v>0.04949588712337006</v>
+      </c>
+      <c r="J43">
+        <v>0.02090635150671005</v>
+      </c>
+      <c r="K43">
+        <v>0.1348825693130493</v>
+      </c>
+      <c r="L43">
+        <v>0.1058972328901291</v>
+      </c>
+      <c r="M43">
+        <v>1.196603298187256</v>
+      </c>
+      <c r="N43" t="s">
+        <v>152</v>
+      </c>
+      <c r="O43" t="s">
+        <v>212</v>
+      </c>
+      <c r="P43" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002839321178255606</v>
+      </c>
+      <c r="D44">
+        <v>0.0001035527602653019</v>
+      </c>
+      <c r="E44">
+        <v>0.002269804943352938</v>
+      </c>
+      <c r="F44">
+        <v>0.001399958040565252</v>
+      </c>
+      <c r="G44">
+        <v>0.001310320687480271</v>
+      </c>
+      <c r="H44">
+        <v>1.000000118636635</v>
+      </c>
+      <c r="I44">
+        <v>0.04958265996175316</v>
+      </c>
+      <c r="J44">
+        <v>0.04562187567353249</v>
+      </c>
+      <c r="K44">
+        <v>0.4040384292602539</v>
+      </c>
+      <c r="L44">
+        <v>0.1299153566360474</v>
+      </c>
+      <c r="M44">
+        <v>2.611229658126831</v>
+      </c>
+      <c r="N44" t="s">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s">
+        <v>213</v>
+      </c>
+      <c r="P44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0004736499601538867</v>
+      </c>
+      <c r="D45">
+        <v>0.0004768617218360305</v>
+      </c>
+      <c r="E45">
+        <v>0.001767763285897672</v>
+      </c>
+      <c r="F45">
+        <v>0.001751061645336449</v>
+      </c>
+      <c r="G45">
+        <v>0.001633655978366733</v>
+      </c>
+      <c r="H45">
+        <v>1.00010606085006</v>
+      </c>
+      <c r="I45">
+        <v>0.04979758528271778</v>
+      </c>
+      <c r="J45">
+        <v>0.2697542905807495</v>
+      </c>
+      <c r="K45">
+        <v>3.767138481140137</v>
+      </c>
+      <c r="L45">
+        <v>0.1011803224682808</v>
+      </c>
+      <c r="M45">
+        <v>15.43975162506104</v>
+      </c>
+      <c r="N45" t="s">
+        <v>154</v>
+      </c>
+      <c r="O45" t="s">
+        <v>214</v>
+      </c>
+      <c r="P45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0007601218206739594</v>
+      </c>
+      <c r="D46">
+        <v>0.0007031895802356303</v>
+      </c>
+      <c r="E46">
+        <v>0.002420250326395035</v>
+      </c>
+      <c r="F46">
+        <v>0.002263984410092235</v>
+      </c>
+      <c r="G46">
+        <v>0.002093814779073</v>
+      </c>
+      <c r="H46">
+        <v>1.00035109683297</v>
+      </c>
+      <c r="I46">
+        <v>0.04986684641392398</v>
+      </c>
+      <c r="J46">
+        <v>0.2905441522598267</v>
+      </c>
+      <c r="K46">
+        <v>9.003396034240723</v>
+      </c>
+      <c r="L46">
+        <v>0.1385262906551361</v>
+      </c>
+      <c r="M46">
+        <v>16.62968635559082</v>
+      </c>
+      <c r="N46" t="s">
+        <v>155</v>
+      </c>
+      <c r="O46" t="s">
+        <v>215</v>
+      </c>
+      <c r="P46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.001221837345879581</v>
+      </c>
+      <c r="D47">
+        <v>0.001023313961923122</v>
+      </c>
+      <c r="E47">
+        <v>0.004573546350002289</v>
+      </c>
+      <c r="F47">
+        <v>0.002684798091650009</v>
+      </c>
+      <c r="G47">
+        <v>0.002527232747524977</v>
+      </c>
+      <c r="H47">
+        <v>1.00077508272739</v>
+      </c>
+      <c r="I47">
+        <v>0.04933271184810332</v>
+      </c>
+      <c r="J47">
+        <v>0.22374626994133</v>
+      </c>
+      <c r="K47">
+        <v>27.51962280273438</v>
+      </c>
+      <c r="L47">
+        <v>0.2617731094360352</v>
+      </c>
+      <c r="M47">
+        <v>12.80642032623291</v>
+      </c>
+      <c r="N47" t="s">
+        <v>156</v>
+      </c>
+      <c r="O47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P47" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.002412500563268613</v>
+      </c>
+      <c r="D48">
+        <v>0.001724749919958413</v>
+      </c>
+      <c r="E48">
+        <v>0.01113298814743757</v>
+      </c>
+      <c r="F48">
+        <v>0.003037821035832167</v>
+      </c>
+      <c r="G48">
+        <v>0.002973310649394989</v>
+      </c>
+      <c r="H48">
+        <v>1.001619339799399</v>
+      </c>
+      <c r="I48">
+        <v>0.04974117553980646</v>
+      </c>
+      <c r="J48">
+        <v>0.1549224555492401</v>
+      </c>
+      <c r="K48">
+        <v>281.9629211425781</v>
+      </c>
+      <c r="L48">
+        <v>0.6372116208076477</v>
+      </c>
+      <c r="M48">
+        <v>8.867196083068848</v>
+      </c>
+      <c r="N48" t="s">
+        <v>157</v>
+      </c>
+      <c r="O48" t="s">
+        <v>217</v>
+      </c>
+      <c r="P48" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.004266014910935781</v>
+      </c>
+      <c r="D49">
+        <v>0.002760737435892224</v>
+      </c>
+      <c r="E49">
+        <v>0.02185407467186451</v>
+      </c>
+      <c r="F49">
+        <v>0.003267180407419801</v>
+      </c>
+      <c r="G49">
+        <v>0.003280831966549158</v>
+      </c>
+      <c r="H49">
+        <v>1.001902446527392</v>
+      </c>
+      <c r="I49">
+        <v>0.05033713978203393</v>
+      </c>
+      <c r="J49">
+        <v>0.1263259798288345</v>
+      </c>
+      <c r="K49">
+        <v>8364.0205078125</v>
+      </c>
+      <c r="L49">
+        <v>1.250847458839417</v>
+      </c>
+      <c r="M49">
+        <v>7.230438232421875</v>
+      </c>
+      <c r="N49" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" t="s">
+        <v>218</v>
+      </c>
+      <c r="P49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.009836928364314426</v>
+      </c>
+      <c r="D50">
+        <v>0.005749230738729239</v>
+      </c>
+      <c r="E50">
+        <v>0.05678502097725868</v>
+      </c>
+      <c r="F50">
+        <v>0.003547787899151444</v>
+      </c>
+      <c r="G50">
+        <v>0.003608416765928268</v>
+      </c>
+      <c r="H50">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I50">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J50">
+        <v>0.1012455523014069</v>
+      </c>
+      <c r="K50">
+        <v>143311040</v>
+      </c>
+      <c r="L50">
+        <v>3.250167369842529</v>
+      </c>
+      <c r="M50">
+        <v>5.794926166534424</v>
+      </c>
+      <c r="N50" t="s">
+        <v>159</v>
+      </c>
+      <c r="O50" t="s">
+        <v>219</v>
+      </c>
+      <c r="P50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01845162468724489</v>
+      </c>
+      <c r="D51">
+        <v>0.01034657284617424</v>
+      </c>
+      <c r="E51">
+        <v>0.1066360920667648</v>
+      </c>
+      <c r="F51">
+        <v>0.003771254327148199</v>
+      </c>
+      <c r="G51">
+        <v>0.003909232094883919</v>
+      </c>
+      <c r="H51">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I51">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J51">
+        <v>0.09702692925930023</v>
+      </c>
+      <c r="K51">
+        <v>441451603296256</v>
+      </c>
+      <c r="L51">
+        <v>6.103460788726807</v>
+      </c>
+      <c r="M51">
+        <v>5.553467273712158</v>
+      </c>
+      <c r="N51" t="s">
+        <v>160</v>
+      </c>
+      <c r="O51" t="s">
+        <v>220</v>
+      </c>
+      <c r="P51" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001987897020806189</v>
+      </c>
+      <c r="D52">
+        <v>0.0002681316691450775</v>
+      </c>
+      <c r="E52">
+        <v>0.0005256053991615772</v>
+      </c>
+      <c r="F52">
+        <v>0.001229616464115679</v>
+      </c>
+      <c r="G52">
+        <v>0.00122786674182862</v>
+      </c>
+      <c r="H52">
+        <v>0.9992924785525057</v>
+      </c>
+      <c r="I52">
+        <v>0.05007633079586019</v>
+      </c>
+      <c r="J52">
+        <v>0.5101387500762939</v>
+      </c>
+      <c r="K52">
+        <v>1.406524181365967</v>
+      </c>
+      <c r="L52">
+        <v>0.03008373454213142</v>
+      </c>
+      <c r="M52">
+        <v>29.1984806060791</v>
+      </c>
+      <c r="N52" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" t="s">
+        <v>221</v>
+      </c>
+      <c r="P52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0002433635780437529</v>
+      </c>
+      <c r="D53">
+        <v>0.0003233589814044535</v>
+      </c>
+      <c r="E53">
+        <v>0.0005898912786506116</v>
+      </c>
+      <c r="F53">
+        <v>0.001340121729299426</v>
+      </c>
+      <c r="G53">
+        <v>0.001345986034721136</v>
+      </c>
+      <c r="H53">
+        <v>0.9992838697320354</v>
+      </c>
+      <c r="I53">
+        <v>0.05017234688873831</v>
+      </c>
+      <c r="J53">
+        <v>0.5481671094894409</v>
+      </c>
+      <c r="K53">
+        <v>1.884454011917114</v>
+      </c>
+      <c r="L53">
+        <v>0.03376322612166405</v>
+      </c>
+      <c r="M53">
+        <v>31.37508583068848</v>
+      </c>
+      <c r="N53" t="s">
+        <v>162</v>
+      </c>
+      <c r="O53" t="s">
+        <v>222</v>
+      </c>
+      <c r="P53" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0002795872723291059</v>
+      </c>
+      <c r="D54">
+        <v>0.0003666891134344041</v>
+      </c>
+      <c r="E54">
+        <v>0.0006322723347693682</v>
+      </c>
+      <c r="F54">
+        <v>0.001410922734066844</v>
+      </c>
+      <c r="G54">
+        <v>0.001414797152392566</v>
+      </c>
+      <c r="H54">
+        <v>0.9993114202800086</v>
+      </c>
+      <c r="I54">
+        <v>0.05028558662967602</v>
+      </c>
+      <c r="J54">
+        <v>0.5799543857574463</v>
+      </c>
+      <c r="K54">
+        <v>2.323601484298706</v>
+      </c>
+      <c r="L54">
+        <v>0.03618896007537842</v>
+      </c>
+      <c r="M54">
+        <v>33.19447326660156</v>
+      </c>
+      <c r="N54" t="s">
+        <v>163</v>
+      </c>
+      <c r="O54" t="s">
+        <v>223</v>
+      </c>
+      <c r="P54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.000399242406131564</v>
+      </c>
+      <c r="D55">
+        <v>0.0005121284048072994</v>
+      </c>
+      <c r="E55">
+        <v>0.00075618049595505</v>
+      </c>
+      <c r="F55">
+        <v>0.001766760251484811</v>
+      </c>
+      <c r="G55">
+        <v>0.001773443189449608</v>
+      </c>
+      <c r="H55">
+        <v>0.9995770841487583</v>
+      </c>
+      <c r="I55">
+        <v>0.05036315264435675</v>
+      </c>
+      <c r="J55">
+        <v>0.6772568225860596</v>
+      </c>
+      <c r="K55">
+        <v>4.351012706756592</v>
+      </c>
+      <c r="L55">
+        <v>0.04328101128339767</v>
+      </c>
+      <c r="M55">
+        <v>38.76371002197266</v>
+      </c>
+      <c r="N55" t="s">
+        <v>164</v>
+      </c>
+      <c r="O55" t="s">
+        <v>224</v>
+      </c>
+      <c r="P55" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0005218663334828791</v>
+      </c>
+      <c r="D56">
+        <v>0.0006531896651722491</v>
+      </c>
+      <c r="E56">
+        <v>0.0009182109497487545</v>
+      </c>
+      <c r="F56">
+        <v>0.002259458182379603</v>
+      </c>
+      <c r="G56">
+        <v>0.002325002569705248</v>
+      </c>
+      <c r="H56">
+        <v>1.000138603231407</v>
+      </c>
+      <c r="I56">
+        <v>0.05026189941688647</v>
+      </c>
+      <c r="J56">
+        <v>0.7113721370697021</v>
+      </c>
+      <c r="K56">
+        <v>7.491056442260742</v>
+      </c>
+      <c r="L56">
+        <v>0.05255504325032234</v>
+      </c>
+      <c r="M56">
+        <v>40.71634674072266</v>
+      </c>
+      <c r="N56" t="s">
+        <v>165</v>
+      </c>
+      <c r="O56" t="s">
+        <v>225</v>
+      </c>
+      <c r="P56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0006348737033005117</v>
+      </c>
+      <c r="D57">
+        <v>0.0007612555637024343</v>
+      </c>
+      <c r="E57">
+        <v>0.001080227666534483</v>
+      </c>
+      <c r="F57">
+        <v>0.002602297347038984</v>
+      </c>
+      <c r="G57">
+        <v>0.002684645354747772</v>
+      </c>
+      <c r="H57">
+        <v>1.000880856332798</v>
+      </c>
+      <c r="I57">
+        <v>0.04926392951822033</v>
+      </c>
+      <c r="J57">
+        <v>0.7047176957130432</v>
+      </c>
+      <c r="K57">
+        <v>11.09719276428223</v>
+      </c>
+      <c r="L57">
+        <v>0.06182828918099403</v>
+      </c>
+      <c r="M57">
+        <v>40.33546829223633</v>
+      </c>
+      <c r="N57" t="s">
+        <v>166</v>
+      </c>
+      <c r="O57" t="s">
+        <v>226</v>
+      </c>
+      <c r="P57" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0007640671660486253</v>
+      </c>
+      <c r="D58">
+        <v>0.0009082391043193638</v>
+      </c>
+      <c r="E58">
+        <v>0.001426167436875403</v>
+      </c>
+      <c r="F58">
+        <v>0.003014741698279977</v>
+      </c>
+      <c r="G58">
+        <v>0.003125736024230719</v>
+      </c>
+      <c r="H58">
+        <v>1.001429391775886</v>
+      </c>
+      <c r="I58">
+        <v>0.04957436408373182</v>
+      </c>
+      <c r="J58">
+        <v>0.6368390321731567</v>
+      </c>
+      <c r="K58">
+        <v>18.5718994140625</v>
+      </c>
+      <c r="L58">
+        <v>0.08162862062454224</v>
+      </c>
+      <c r="M58">
+        <v>36.45034408569336</v>
+      </c>
+      <c r="N58" t="s">
+        <v>167</v>
+      </c>
+      <c r="O58" t="s">
+        <v>227</v>
+      </c>
+      <c r="P58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0008519436163874717</v>
+      </c>
+      <c r="D59">
+        <v>0.00101702066604048</v>
+      </c>
+      <c r="E59">
+        <v>0.001987143186852336</v>
+      </c>
+      <c r="F59">
+        <v>0.003274244954809546</v>
+      </c>
+      <c r="G59">
+        <v>0.003431444987654686</v>
+      </c>
+      <c r="H59">
+        <v>1.00172245053861</v>
+      </c>
+      <c r="I59">
+        <v>0.05010924923599727</v>
+      </c>
+      <c r="J59">
+        <v>0.5118004083633423</v>
+      </c>
+      <c r="K59">
+        <v>26.93597793579102</v>
+      </c>
+      <c r="L59">
+        <v>0.1137368232011795</v>
+      </c>
+      <c r="M59">
+        <v>29.29358863830566</v>
+      </c>
+      <c r="N59" t="s">
+        <v>168</v>
+      </c>
+      <c r="O59" t="s">
+        <v>228</v>
+      </c>
+      <c r="P59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0009611544618207653</v>
+      </c>
+      <c r="D60">
+        <v>0.001192900002934039</v>
+      </c>
+      <c r="E60">
+        <v>0.003181792097166181</v>
+      </c>
+      <c r="F60">
+        <v>0.003488411195576191</v>
+      </c>
+      <c r="G60">
+        <v>0.003705990733578801</v>
+      </c>
+      <c r="H60">
+        <v>1.002548125069545</v>
+      </c>
+      <c r="I60">
+        <v>0.05593986455170138</v>
+      </c>
+      <c r="J60">
+        <v>0.3749144971370697</v>
+      </c>
+      <c r="K60">
+        <v>48.68489074707031</v>
+      </c>
+      <c r="L60">
+        <v>0.1821141690015793</v>
+      </c>
+      <c r="M60">
+        <v>21.45873832702637</v>
+      </c>
+      <c r="N60" t="s">
+        <v>169</v>
+      </c>
+      <c r="O60" t="s">
+        <v>229</v>
+      </c>
+      <c r="P60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.001039286703912782</v>
+      </c>
+      <c r="D61">
+        <v>0.001385654439218342</v>
+      </c>
+      <c r="E61">
+        <v>0.004384593572467566</v>
+      </c>
+      <c r="F61">
+        <v>0.003618272487074137</v>
+      </c>
+      <c r="G61">
+        <v>0.003954130224883556</v>
+      </c>
+      <c r="H61">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I61">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J61">
+        <v>0.3160280287265778</v>
+      </c>
+      <c r="K61">
+        <v>92.35170745849609</v>
+      </c>
+      <c r="L61">
+        <v>0.2509581446647644</v>
+      </c>
+      <c r="M61">
+        <v>18.08829116821289</v>
+      </c>
+      <c r="N61" t="s">
+        <v>170</v>
+      </c>
+      <c r="O61" t="s">
+        <v>230</v>
+      </c>
+      <c r="P61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.000785029927442523</v>
+      </c>
+      <c r="D2">
+        <v>-0.004670889116823673</v>
+      </c>
+      <c r="E2">
+        <v>0.09096690267324448</v>
+      </c>
+      <c r="F2">
+        <v>0.0008763581863604486</v>
+      </c>
+      <c r="G2">
+        <v>0.0009287804714404047</v>
+      </c>
+      <c r="H2">
+        <v>1.00032443181982</v>
+      </c>
+      <c r="I2">
+        <v>0.04907650076394903</v>
+      </c>
+      <c r="J2">
+        <v>-0.05134712532162666</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999997615814209</v>
+      </c>
+      <c r="L2">
+        <v>5.206613540649414</v>
+      </c>
+      <c r="M2">
+        <v>-2.938922166824341</v>
+      </c>
+      <c r="N2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.001045421109693543</v>
+      </c>
+      <c r="D3">
+        <v>-0.006319967098534107</v>
+      </c>
+      <c r="E3">
+        <v>0.1267021745443344</v>
+      </c>
+      <c r="F3">
+        <v>0.001045139040797949</v>
+      </c>
+      <c r="G3">
+        <v>0.00102478708140552</v>
+      </c>
+      <c r="H3">
+        <v>1.000504607566638</v>
+      </c>
+      <c r="I3">
+        <v>0.04900885549657205</v>
+      </c>
+      <c r="J3">
+        <v>-0.0498804934322834</v>
+      </c>
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3">
+        <v>7.251970291137695</v>
+      </c>
+      <c r="M3">
+        <v>-2.854977369308472</v>
+      </c>
+      <c r="N3" t="s">
+        <v>292</v>
+      </c>
+      <c r="O3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001303795498199316</v>
+      </c>
+      <c r="D4">
+        <v>-0.002344211796298623</v>
+      </c>
+      <c r="E4">
+        <v>0.05850798636674881</v>
+      </c>
+      <c r="F4">
+        <v>0.001183836720883846</v>
+      </c>
+      <c r="G4">
+        <v>0.001155668986029923</v>
+      </c>
+      <c r="H4">
+        <v>1.000574083074721</v>
+      </c>
+      <c r="I4">
+        <v>0.04903080577650402</v>
+      </c>
+      <c r="J4">
+        <v>-0.04006652534008026</v>
+      </c>
+      <c r="K4">
+        <v>-0.9995419979095459</v>
+      </c>
+      <c r="L4">
+        <v>3.348783731460571</v>
+      </c>
+      <c r="M4">
+        <v>-2.293261766433716</v>
+      </c>
+      <c r="N4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002565546488406263</v>
+      </c>
+      <c r="D5">
+        <v>-0.002156569855287671</v>
+      </c>
+      <c r="E5">
+        <v>0.07345239073038101</v>
+      </c>
+      <c r="F5">
+        <v>0.00159362331032753</v>
+      </c>
+      <c r="G5">
+        <v>0.001493634423241019</v>
+      </c>
+      <c r="H5">
+        <v>1.000691803529323</v>
+      </c>
+      <c r="I5">
+        <v>0.04915996548500285</v>
+      </c>
+      <c r="J5">
+        <v>-0.02936010435223579</v>
+      </c>
+      <c r="K5">
+        <v>-0.999151885509491</v>
+      </c>
+      <c r="L5">
+        <v>4.204146862030029</v>
+      </c>
+      <c r="M5">
+        <v>-1.680465221405029</v>
+      </c>
+      <c r="N5" t="s">
+        <v>294</v>
+      </c>
+      <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.005018740793131277</v>
+      </c>
+      <c r="D6">
+        <v>0.001668724231421947</v>
+      </c>
+      <c r="E6">
+        <v>0.03099222294986248</v>
+      </c>
+      <c r="F6">
+        <v>0.002010908210650086</v>
+      </c>
+      <c r="G6">
+        <v>0.001865805825218558</v>
+      </c>
+      <c r="H6">
+        <v>1.000829477603836</v>
+      </c>
+      <c r="I6">
+        <v>0.04935590674741826</v>
+      </c>
+      <c r="J6">
+        <v>0.05384332314133644</v>
+      </c>
+      <c r="K6">
+        <v>234.5864105224609</v>
+      </c>
+      <c r="L6">
+        <v>1.773881793022156</v>
+      </c>
+      <c r="M6">
+        <v>3.081795454025269</v>
+      </c>
+      <c r="N6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O6" t="s">
+        <v>355</v>
+      </c>
+      <c r="P6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.009844258942128519</v>
+      </c>
+      <c r="D7">
+        <v>0.005134913604706526</v>
+      </c>
+      <c r="E7">
+        <v>0.03521668910980225</v>
+      </c>
+      <c r="F7">
+        <v>0.002469044644385576</v>
+      </c>
+      <c r="G7">
+        <v>0.00228855200111866</v>
+      </c>
+      <c r="H7">
+        <v>1.00102725407983</v>
+      </c>
+      <c r="I7">
+        <v>0.0491439315304583</v>
+      </c>
+      <c r="J7">
+        <v>0.1458090990781784</v>
+      </c>
+      <c r="K7">
+        <v>19365836</v>
+      </c>
+      <c r="L7">
+        <v>2.015674829483032</v>
+      </c>
+      <c r="M7">
+        <v>8.3455810546875</v>
+      </c>
+      <c r="N7" t="s">
+        <v>296</v>
+      </c>
+      <c r="O7" t="s">
+        <v>356</v>
+      </c>
+      <c r="P7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02411041049581981</v>
+      </c>
+      <c r="D8">
+        <v>0.01259514130651951</v>
+      </c>
+      <c r="E8">
+        <v>0.0878579169511795</v>
+      </c>
+      <c r="F8">
+        <v>0.002890694886445999</v>
+      </c>
+      <c r="G8">
+        <v>0.002716220216825604</v>
+      </c>
+      <c r="H8">
+        <v>1.001494421423279</v>
+      </c>
+      <c r="I8">
+        <v>0.04983799969664835</v>
+      </c>
+      <c r="J8">
+        <v>0.1433580666780472</v>
+      </c>
+      <c r="K8">
+        <v>6.424790038478848E+17</v>
+      </c>
+      <c r="L8">
+        <v>5.028666496276855</v>
+      </c>
+      <c r="M8">
+        <v>8.205292701721191</v>
+      </c>
+      <c r="N8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O8" t="s">
+        <v>357</v>
+      </c>
+      <c r="P8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.04775922500186986</v>
+      </c>
+      <c r="D9">
+        <v>0.02536341920495033</v>
+      </c>
+      <c r="E9">
+        <v>0.1894807368516922</v>
+      </c>
+      <c r="F9">
+        <v>0.003162337932735682</v>
+      </c>
+      <c r="G9">
+        <v>0.003025884740054607</v>
+      </c>
+      <c r="H9">
+        <v>1.001778290502006</v>
+      </c>
+      <c r="I9">
+        <v>0.0505734551564947</v>
+      </c>
+      <c r="J9">
+        <v>0.1338575035333633</v>
+      </c>
+      <c r="K9">
+        <v>4.322877505945859E+35</v>
+      </c>
+      <c r="L9">
+        <v>10.84518623352051</v>
+      </c>
+      <c r="M9">
+        <v>7.661515235900879</v>
+      </c>
+      <c r="N9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1199439931715914</v>
+      </c>
+      <c r="D10">
+        <v>0.06389252096414566</v>
+      </c>
+      <c r="E10">
+        <v>0.500178337097168</v>
+      </c>
+      <c r="F10">
+        <v>0.003483912209048867</v>
+      </c>
+      <c r="G10">
+        <v>0.003427732968702912</v>
+      </c>
+      <c r="H10">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I10">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J10">
+        <v>0.1277394741773605</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>28.62838363647461</v>
+      </c>
+      <c r="M10">
+        <v>7.311341285705566</v>
+      </c>
+      <c r="N10" t="s">
+        <v>299</v>
+      </c>
+      <c r="O10" t="s">
+        <v>359</v>
+      </c>
+      <c r="P10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.2323125027200634</v>
+      </c>
+      <c r="D11">
+        <v>0.1259126663208008</v>
+      </c>
+      <c r="E11">
+        <v>0.9756034016609192</v>
+      </c>
+      <c r="F11">
+        <v>0.0036844068672508</v>
+      </c>
+      <c r="G11">
+        <v>0.003691644174978137</v>
+      </c>
+      <c r="H11">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I11">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J11">
+        <v>0.1290613263845444</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>55.8399772644043</v>
+      </c>
+      <c r="M11">
+        <v>7.386999607086182</v>
+      </c>
+      <c r="N11" t="s">
+        <v>300</v>
+      </c>
+      <c r="O11" t="s">
+        <v>360</v>
+      </c>
+      <c r="P11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001266927492946326</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002502782153896987</v>
+      </c>
+      <c r="E12">
+        <v>0.009740513749420643</v>
+      </c>
+      <c r="F12">
+        <v>0.0008971648057922721</v>
+      </c>
+      <c r="G12">
+        <v>0.0009395428351126611</v>
+      </c>
+      <c r="H12">
+        <v>1.000270105857431</v>
+      </c>
+      <c r="I12">
+        <v>0.04913247814723159</v>
+      </c>
+      <c r="J12">
+        <v>-0.02569456025958061</v>
+      </c>
+      <c r="K12">
+        <v>-0.5595769882202148</v>
+      </c>
+      <c r="L12">
+        <v>0.5575114488601685</v>
+      </c>
+      <c r="M12">
+        <v>-1.470662832260132</v>
+      </c>
+      <c r="N12" t="s">
+        <v>301</v>
+      </c>
+      <c r="O12" t="s">
+        <v>361</v>
+      </c>
+      <c r="P12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.001687394780070009</v>
+      </c>
+      <c r="D13">
+        <v>0.0001295987021876499</v>
+      </c>
+      <c r="E13">
+        <v>0.01204245816916227</v>
+      </c>
+      <c r="F13">
+        <v>0.001079298672266304</v>
+      </c>
+      <c r="G13">
+        <v>0.001049293554387987</v>
+      </c>
+      <c r="H13">
+        <v>1.000428375359907</v>
+      </c>
+      <c r="I13">
+        <v>0.049096659843749</v>
+      </c>
+      <c r="J13">
+        <v>0.01076181419193745</v>
+      </c>
+      <c r="K13">
+        <v>0.5287925004959106</v>
+      </c>
+      <c r="L13">
+        <v>0.6892663836479187</v>
+      </c>
+      <c r="M13">
+        <v>0.6159669756889343</v>
+      </c>
+      <c r="N13" t="s">
+        <v>302</v>
+      </c>
+      <c r="O13" t="s">
+        <v>362</v>
+      </c>
+      <c r="P13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002104925593849302</v>
+      </c>
+      <c r="D14">
+        <v>0.0006732222391292453</v>
+      </c>
+      <c r="E14">
+        <v>0.01358231343328953</v>
+      </c>
+      <c r="F14">
+        <v>0.001225645537488163</v>
+      </c>
+      <c r="G14">
+        <v>0.001170523115433753</v>
+      </c>
+      <c r="H14">
+        <v>1.00047263606747</v>
+      </c>
+      <c r="I14">
+        <v>0.04914184725160682</v>
+      </c>
+      <c r="J14">
+        <v>0.04956609383225441</v>
+      </c>
+      <c r="K14">
+        <v>8.066432952880859</v>
+      </c>
+      <c r="L14">
+        <v>0.7774020433425903</v>
+      </c>
+      <c r="M14">
+        <v>2.836982250213623</v>
+      </c>
+      <c r="N14" t="s">
+        <v>303</v>
+      </c>
+      <c r="O14" t="s">
+        <v>363</v>
+      </c>
+      <c r="P14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.004162561712603926</v>
+      </c>
+      <c r="D15">
+        <v>0.002377406228333712</v>
+      </c>
+      <c r="E15">
+        <v>0.03178749606013298</v>
+      </c>
+      <c r="F15">
+        <v>0.001628688303753734</v>
+      </c>
+      <c r="G15">
+        <v>0.001532955793663859</v>
+      </c>
+      <c r="H15">
+        <v>1.000620672805615</v>
+      </c>
+      <c r="I15">
+        <v>0.04925013299149386</v>
+      </c>
+      <c r="J15">
+        <v>0.07479061186313629</v>
+      </c>
+      <c r="K15">
+        <v>2389.096923828125</v>
+      </c>
+      <c r="L15">
+        <v>1.819400310516357</v>
+      </c>
+      <c r="M15">
+        <v>4.280741691589355</v>
+      </c>
+      <c r="N15" t="s">
+        <v>304</v>
+      </c>
+      <c r="O15" t="s">
+        <v>364</v>
+      </c>
+      <c r="P15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.008201652321919573</v>
+      </c>
+      <c r="D16">
+        <v>0.004661263432353735</v>
+      </c>
+      <c r="E16">
+        <v>0.04062195867300034</v>
+      </c>
+      <c r="F16">
+        <v>0.002082698978483677</v>
+      </c>
+      <c r="G16">
+        <v>0.001939987647347152</v>
+      </c>
+      <c r="H16">
+        <v>1.000759386999425</v>
+      </c>
+      <c r="I16">
+        <v>0.04942165021082656</v>
+      </c>
+      <c r="J16">
+        <v>0.1147473827004433</v>
+      </c>
+      <c r="K16">
+        <v>4135047.25</v>
+      </c>
+      <c r="L16">
+        <v>2.325052738189697</v>
+      </c>
+      <c r="M16">
+        <v>6.567721366882324</v>
+      </c>
+      <c r="N16" t="s">
+        <v>305</v>
+      </c>
+      <c r="O16" t="s">
+        <v>365</v>
+      </c>
+      <c r="P16" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.0161719547802058</v>
+      </c>
+      <c r="D17">
+        <v>0.00910825002938509</v>
+      </c>
+      <c r="E17">
+        <v>0.07458408176898956</v>
+      </c>
+      <c r="F17">
+        <v>0.002533094258978963</v>
+      </c>
+      <c r="G17">
+        <v>0.002337160054594278</v>
+      </c>
+      <c r="H17">
+        <v>1.001014803089684</v>
+      </c>
+      <c r="I17">
+        <v>0.04912639288542517</v>
+      </c>
+      <c r="J17">
+        <v>0.1221205592155457</v>
+      </c>
+      <c r="K17">
+        <v>7946368974848</v>
+      </c>
+      <c r="L17">
+        <v>4.2689208984375</v>
+      </c>
+      <c r="M17">
+        <v>6.989735126495361</v>
+      </c>
+      <c r="N17" t="s">
+        <v>306</v>
+      </c>
+      <c r="O17" t="s">
+        <v>366</v>
+      </c>
+      <c r="P17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.03995417343120478</v>
+      </c>
+      <c r="D18">
+        <v>0.0210268460214138</v>
+      </c>
+      <c r="E18">
+        <v>0.1623516082763672</v>
+      </c>
+      <c r="F18">
+        <v>0.002940521575510502</v>
+      </c>
+      <c r="G18">
+        <v>0.002765585668385029</v>
+      </c>
+      <c r="H18">
+        <v>1.001499103478249</v>
+      </c>
+      <c r="I18">
+        <v>0.04983330815167534</v>
+      </c>
+      <c r="J18">
+        <v>0.1295142471790314</v>
+      </c>
+      <c r="K18">
+        <v>4.034087612620492E+29</v>
+      </c>
+      <c r="L18">
+        <v>9.292413711547852</v>
+      </c>
+      <c r="M18">
+        <v>7.412922859191895</v>
+      </c>
+      <c r="N18" t="s">
+        <v>307</v>
+      </c>
+      <c r="O18" t="s">
+        <v>367</v>
+      </c>
+      <c r="P18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.07878389954484807</v>
+      </c>
+      <c r="D19">
+        <v>0.04033636301755905</v>
+      </c>
+      <c r="E19">
+        <v>0.3041417300701141</v>
+      </c>
+      <c r="F19">
+        <v>0.003171501681208611</v>
+      </c>
+      <c r="G19">
+        <v>0.003048798302188516</v>
+      </c>
+      <c r="H19">
+        <v>1.001803345489537</v>
+      </c>
+      <c r="I19">
+        <v>0.05031258446840677</v>
+      </c>
+      <c r="J19">
+        <v>0.1326235681772232</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>17.40796279907227</v>
+      </c>
+      <c r="M19">
+        <v>7.590888977050781</v>
+      </c>
+      <c r="N19" t="s">
+        <v>308</v>
+      </c>
+      <c r="O19" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.1977733539583726</v>
+      </c>
+      <c r="D20">
+        <v>0.1016796454787254</v>
+      </c>
+      <c r="E20">
+        <v>0.8069943189620972</v>
+      </c>
+      <c r="F20">
+        <v>0.003518480807542801</v>
+      </c>
+      <c r="G20">
+        <v>0.003446159418672323</v>
+      </c>
+      <c r="H20">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I20">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J20">
+        <v>0.1259979754686356</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>46.18941116333008</v>
+      </c>
+      <c r="M20">
+        <v>7.211664199829102</v>
+      </c>
+      <c r="N20" t="s">
+        <v>309</v>
+      </c>
+      <c r="O20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.3863856631396306</v>
+      </c>
+      <c r="D21">
+        <v>0.2089311331510544</v>
+      </c>
+      <c r="E21">
+        <v>1.701594829559326</v>
+      </c>
+      <c r="F21">
+        <v>0.00368379894644022</v>
+      </c>
+      <c r="G21">
+        <v>0.003740479005500674</v>
+      </c>
+      <c r="H21">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I21">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J21">
+        <v>0.1227854788303375</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>97.39308166503906</v>
+      </c>
+      <c r="M21">
+        <v>7.027792930603027</v>
+      </c>
+      <c r="N21" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" t="s">
+        <v>370</v>
+      </c>
+      <c r="P21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0003441998844036652</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003955700085498393</v>
+      </c>
+      <c r="E22">
+        <v>0.001864715246483684</v>
+      </c>
+      <c r="F22">
+        <v>0.0009462441666983068</v>
+      </c>
+      <c r="G22">
+        <v>0.000968565174844116</v>
+      </c>
+      <c r="H22">
+        <v>1.000159845207143</v>
+      </c>
+      <c r="I22">
+        <v>0.04919095887687452</v>
+      </c>
+      <c r="J22">
+        <v>-0.2121342718601227</v>
+      </c>
+      <c r="K22">
+        <v>-0.7264385223388672</v>
+      </c>
+      <c r="L22">
+        <v>0.1067294999957085</v>
+      </c>
+      <c r="M22">
+        <v>-12.14179134368896</v>
+      </c>
+      <c r="N22" t="s">
+        <v>311</v>
+      </c>
+      <c r="O22" t="s">
+        <v>371</v>
+      </c>
+      <c r="P22" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0004558872775484409</v>
+      </c>
+      <c r="D23">
+        <v>-0.0001646917808102444</v>
+      </c>
+      <c r="E23">
+        <v>0.001991117373108864</v>
+      </c>
+      <c r="F23">
+        <v>0.001133119105361402</v>
+      </c>
+      <c r="G23">
+        <v>0.001090262900106609</v>
+      </c>
+      <c r="H23">
+        <v>1.000331918224226</v>
+      </c>
+      <c r="I23">
+        <v>0.04918716655921088</v>
+      </c>
+      <c r="J23">
+        <v>-0.08271324634552002</v>
+      </c>
+      <c r="K23">
+        <v>-0.4169959425926208</v>
+      </c>
+      <c r="L23">
+        <v>0.1139642894268036</v>
+      </c>
+      <c r="M23">
+        <v>-4.734204292297363</v>
+      </c>
+      <c r="N23" t="s">
+        <v>312</v>
+      </c>
+      <c r="O23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0005642122010205462</v>
+      </c>
+      <c r="D24">
+        <v>-5.224330743658356E-05</v>
+      </c>
+      <c r="E24">
+        <v>0.001938623376190662</v>
+      </c>
+      <c r="F24">
+        <v>0.001282220124267042</v>
+      </c>
+      <c r="G24">
+        <v>0.001215992728248239</v>
+      </c>
+      <c r="H24">
+        <v>1.000381664648849</v>
+      </c>
+      <c r="I24">
+        <v>0.04921520008593009</v>
+      </c>
+      <c r="J24">
+        <v>-0.02694866247475147</v>
+      </c>
+      <c r="K24">
+        <v>-0.157226026058197</v>
+      </c>
+      <c r="L24">
+        <v>0.1109597310423851</v>
+      </c>
+      <c r="M24">
+        <v>-1.542443156242371</v>
+      </c>
+      <c r="N24" t="s">
+        <v>313</v>
+      </c>
+      <c r="O24" t="s">
+        <v>373</v>
+      </c>
+      <c r="P24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001070732737504906</v>
+      </c>
+      <c r="D25">
+        <v>0.000430319516453892</v>
+      </c>
+      <c r="E25">
+        <v>0.003319419920444489</v>
+      </c>
+      <c r="F25">
+        <v>0.001667163684032857</v>
+      </c>
+      <c r="G25">
+        <v>0.001573635148815811</v>
+      </c>
+      <c r="H25">
+        <v>1.000502690584184</v>
+      </c>
+      <c r="I25">
+        <v>0.04933645935455525</v>
+      </c>
+      <c r="J25">
+        <v>0.1296369582414627</v>
+      </c>
+      <c r="K25">
+        <v>3.09394359588623</v>
+      </c>
+      <c r="L25">
+        <v>0.1899914890527725</v>
+      </c>
+      <c r="M25">
+        <v>7.419946670532227</v>
+      </c>
+      <c r="N25" t="s">
+        <v>314</v>
+      </c>
+      <c r="O25" t="s">
+        <v>374</v>
+      </c>
+      <c r="P25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.002005607656759874</v>
+      </c>
+      <c r="D26">
+        <v>0.001056338544003665</v>
+      </c>
+      <c r="E26">
+        <v>0.006395607255399227</v>
+      </c>
+      <c r="F26">
+        <v>0.002133053261786699</v>
+      </c>
+      <c r="G26">
+        <v>0.001982674933969975</v>
+      </c>
+      <c r="H26">
+        <v>1.000658529747428</v>
+      </c>
+      <c r="I26">
+        <v>0.04951126663580121</v>
+      </c>
+      <c r="J26">
+        <v>0.1651662588119507</v>
+      </c>
+      <c r="K26">
+        <v>30.77426528930664</v>
+      </c>
+      <c r="L26">
+        <v>0.3660612106323242</v>
+      </c>
+      <c r="M26">
+        <v>9.453514099121094</v>
+      </c>
+      <c r="N26" t="s">
+        <v>315</v>
+      </c>
+      <c r="O26" t="s">
+        <v>375</v>
+      </c>
+      <c r="P26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.003775834039125624</v>
+      </c>
+      <c r="D27">
+        <v>0.002262607216835022</v>
+      </c>
+      <c r="E27">
+        <v>0.0108597232028842</v>
+      </c>
+      <c r="F27">
+        <v>0.002575145103037357</v>
+      </c>
+      <c r="G27">
+        <v>0.002387981628999114</v>
+      </c>
+      <c r="H27">
+        <v>1.001002377331555</v>
+      </c>
+      <c r="I27">
+        <v>0.04912840057187487</v>
+      </c>
+      <c r="J27">
+        <v>0.2083485126495361</v>
+      </c>
+      <c r="K27">
+        <v>1641.34375</v>
+      </c>
+      <c r="L27">
+        <v>0.6215709447860718</v>
+      </c>
+      <c r="M27">
+        <v>11.92510890960693</v>
+      </c>
+      <c r="N27" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" t="s">
+        <v>376</v>
+      </c>
+      <c r="P27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.008920562782236052</v>
+      </c>
+      <c r="D28">
+        <v>0.005150030367076397</v>
+      </c>
+      <c r="E28">
+        <v>0.02727544121444225</v>
+      </c>
+      <c r="F28">
+        <v>0.002988586900755763</v>
+      </c>
+      <c r="G28">
+        <v>0.002810101490467787</v>
+      </c>
+      <c r="H28">
+        <v>1.001514003221512</v>
+      </c>
+      <c r="I28">
+        <v>0.04985377187972336</v>
+      </c>
+      <c r="J28">
+        <v>0.1888156533241272</v>
+      </c>
+      <c r="K28">
+        <v>20345384</v>
+      </c>
+      <c r="L28">
+        <v>1.56114673614502</v>
+      </c>
+      <c r="M28">
+        <v>10.80711936950684</v>
+      </c>
+      <c r="N28" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" t="s">
+        <v>377</v>
+      </c>
+      <c r="P28" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.01730386871084904</v>
+      </c>
+      <c r="D29">
+        <v>0.009801134467124939</v>
+      </c>
+      <c r="E29">
+        <v>0.05484296381473541</v>
+      </c>
+      <c r="F29">
+        <v>0.003206336637958884</v>
+      </c>
+      <c r="G29">
+        <v>0.003097891807556152</v>
+      </c>
+      <c r="H29">
+        <v>1.001829953972321</v>
+      </c>
+      <c r="I29">
+        <v>0.05029435254934062</v>
+      </c>
+      <c r="J29">
+        <v>0.1787127107381821</v>
+      </c>
+      <c r="K29">
+        <v>75279997337600</v>
+      </c>
+      <c r="L29">
+        <v>3.139011144638062</v>
+      </c>
+      <c r="M29">
+        <v>10.22886371612549</v>
+      </c>
+      <c r="N29" t="s">
+        <v>318</v>
+      </c>
+      <c r="O29" t="s">
+        <v>378</v>
+      </c>
+      <c r="P29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.04251209741758166</v>
+      </c>
+      <c r="D30">
+        <v>0.02364590018987656</v>
+      </c>
+      <c r="E30">
+        <v>0.1365143656730652</v>
+      </c>
+      <c r="F30">
+        <v>0.003536055563017726</v>
+      </c>
+      <c r="G30">
+        <v>0.003503917716443539</v>
+      </c>
+      <c r="H30">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I30">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J30">
+        <v>0.1732118129730225</v>
+      </c>
+      <c r="K30">
+        <v>1.78055113193986E+33</v>
+      </c>
+      <c r="L30">
+        <v>7.813584327697754</v>
+      </c>
+      <c r="M30">
+        <v>9.91401195526123</v>
+      </c>
+      <c r="N30" t="s">
+        <v>319</v>
+      </c>
+      <c r="O30" t="s">
+        <v>379</v>
+      </c>
+      <c r="P30" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.08237119938052558</v>
+      </c>
+      <c r="D31">
+        <v>0.04540184885263443</v>
+      </c>
+      <c r="E31">
+        <v>0.2678051292896271</v>
+      </c>
+      <c r="F31">
+        <v>0.0037462436594069</v>
+      </c>
+      <c r="G31">
+        <v>0.003824224462732673</v>
+      </c>
+      <c r="H31">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I31">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J31">
+        <v>0.1695331633090973</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>15.32818794250488</v>
+      </c>
+      <c r="M31">
+        <v>9.703459739685059</v>
+      </c>
+      <c r="N31" t="s">
+        <v>320</v>
+      </c>
+      <c r="O31" t="s">
+        <v>380</v>
+      </c>
+      <c r="P31" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0004261723224925672</v>
+      </c>
+      <c r="D32">
+        <v>-2.0280143871787E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003240161575376987</v>
+      </c>
+      <c r="F32">
+        <v>0.001006266917102039</v>
+      </c>
+      <c r="G32">
+        <v>0.001003719982691109</v>
+      </c>
+      <c r="H32">
+        <v>1.000009571835723</v>
+      </c>
+      <c r="I32">
+        <v>0.04938660919466738</v>
+      </c>
+      <c r="J32">
+        <v>-0.006258991546928883</v>
+      </c>
+      <c r="K32">
+        <v>-0.06423479318618774</v>
+      </c>
+      <c r="L32">
+        <v>0.1854550242424011</v>
+      </c>
+      <c r="M32">
+        <v>-0.3582418262958527</v>
+      </c>
+      <c r="N32" t="s">
+        <v>321</v>
+      </c>
+      <c r="O32" t="s">
+        <v>381</v>
+      </c>
+      <c r="P32" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0005631109631394102</v>
+      </c>
+      <c r="D33">
+        <v>0.0001863700017565861</v>
+      </c>
+      <c r="E33">
+        <v>0.00430406117811799</v>
+      </c>
+      <c r="F33">
+        <v>0.001207194058224559</v>
+      </c>
+      <c r="G33">
+        <v>0.00114339345600456</v>
+      </c>
+      <c r="H33">
+        <v>1.000182808525612</v>
+      </c>
+      <c r="I33">
+        <v>0.04936206908712921</v>
+      </c>
+      <c r="J33">
+        <v>0.04330096393823624</v>
+      </c>
+      <c r="K33">
+        <v>0.8410589694976807</v>
+      </c>
+      <c r="L33">
+        <v>0.2463487535715103</v>
+      </c>
+      <c r="M33">
+        <v>2.478389263153076</v>
+      </c>
+      <c r="N33" t="s">
+        <v>322</v>
+      </c>
+      <c r="O33" t="s">
+        <v>382</v>
+      </c>
+      <c r="P33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0006959094591720498</v>
+      </c>
+      <c r="D34">
+        <v>0.0002265651128254831</v>
+      </c>
+      <c r="E34">
+        <v>0.004546920768916607</v>
+      </c>
+      <c r="F34">
+        <v>0.001341171213425696</v>
+      </c>
+      <c r="G34">
+        <v>0.001256420742720366</v>
+      </c>
+      <c r="H34">
+        <v>1.000248506362933</v>
+      </c>
+      <c r="I34">
+        <v>0.04936561115069341</v>
+      </c>
+      <c r="J34">
+        <v>0.04982824996113777</v>
+      </c>
+      <c r="K34">
+        <v>1.100788354873657</v>
+      </c>
+      <c r="L34">
+        <v>0.2602491676807404</v>
+      </c>
+      <c r="M34">
+        <v>2.85198712348938</v>
+      </c>
+      <c r="N34" t="s">
+        <v>323</v>
+      </c>
+      <c r="O34" t="s">
+        <v>383</v>
+      </c>
+      <c r="P34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001321531734350838</v>
+      </c>
+      <c r="D35">
+        <v>0.0008539059199392796</v>
+      </c>
+      <c r="E35">
+        <v>0.008841937407851219</v>
+      </c>
+      <c r="F35">
+        <v>0.001702869776636362</v>
+      </c>
+      <c r="G35">
+        <v>0.001595059758983552</v>
+      </c>
+      <c r="H35">
+        <v>1.000375962137773</v>
+      </c>
+      <c r="I35">
+        <v>0.04952027388649611</v>
+      </c>
+      <c r="J35">
+        <v>0.09657453000545502</v>
+      </c>
+      <c r="K35">
+        <v>15.38178634643555</v>
+      </c>
+      <c r="L35">
+        <v>0.5060802102088928</v>
+      </c>
+      <c r="M35">
+        <v>5.527573585510254</v>
+      </c>
+      <c r="N35" t="s">
+        <v>324</v>
+      </c>
+      <c r="O35" t="s">
+        <v>384</v>
+      </c>
+      <c r="P35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.002490377367635049</v>
+      </c>
+      <c r="D36">
+        <v>0.001776703167706728</v>
+      </c>
+      <c r="E36">
+        <v>0.01869694329798222</v>
+      </c>
+      <c r="F36">
+        <v>0.002185640623793006</v>
+      </c>
+      <c r="G36">
+        <v>0.00202121795155108</v>
+      </c>
+      <c r="H36">
+        <v>1.000559939702281</v>
+      </c>
+      <c r="I36">
+        <v>0.04969773651223898</v>
+      </c>
+      <c r="J36">
+        <v>0.09502639621496201</v>
+      </c>
+      <c r="K36">
+        <v>334.3883666992188</v>
+      </c>
+      <c r="L36">
+        <v>1.070144772529602</v>
+      </c>
+      <c r="M36">
+        <v>5.438964366912842</v>
+      </c>
+      <c r="N36" t="s">
+        <v>325</v>
+      </c>
+      <c r="O36" t="s">
+        <v>385</v>
+      </c>
+      <c r="P36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.004720646469940097</v>
+      </c>
+      <c r="D37">
+        <v>0.003229845315217972</v>
+      </c>
+      <c r="E37">
+        <v>0.03531990945339203</v>
+      </c>
+      <c r="F37">
+        <v>0.002627946669235826</v>
+      </c>
+      <c r="G37">
+        <v>0.002449126215651631</v>
+      </c>
+      <c r="H37">
+        <v>1.000969179352978</v>
+      </c>
+      <c r="I37">
+        <v>0.04920445872119472</v>
+      </c>
+      <c r="J37">
+        <v>0.09144546091556549</v>
+      </c>
+      <c r="K37">
+        <v>38713.09375</v>
+      </c>
+      <c r="L37">
+        <v>2.021582841873169</v>
+      </c>
+      <c r="M37">
+        <v>5.234004497528076</v>
+      </c>
+      <c r="N37" t="s">
+        <v>326</v>
+      </c>
+      <c r="O37" t="s">
+        <v>386</v>
+      </c>
+      <c r="P37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01124108523257225</v>
+      </c>
+      <c r="D38">
+        <v>0.007240928243845701</v>
+      </c>
+      <c r="E38">
+        <v>0.08421390503644943</v>
+      </c>
+      <c r="F38">
+        <v>0.003043663920834661</v>
+      </c>
+      <c r="G38">
+        <v>0.002881019143387675</v>
+      </c>
+      <c r="H38">
+        <v>1.001556095192137</v>
+      </c>
+      <c r="I38">
+        <v>0.04978973046988632</v>
+      </c>
+      <c r="J38">
+        <v>0.08598257601261139</v>
+      </c>
+      <c r="K38">
+        <v>18401380352</v>
+      </c>
+      <c r="L38">
+        <v>4.820096492767334</v>
+      </c>
+      <c r="M38">
+        <v>4.921329021453857</v>
+      </c>
+      <c r="N38" t="s">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s">
+        <v>387</v>
+      </c>
+      <c r="P38" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02201627874416391</v>
+      </c>
+      <c r="D39">
+        <v>0.01447920687496662</v>
+      </c>
+      <c r="E39">
+        <v>0.1832647025585175</v>
+      </c>
+      <c r="F39">
+        <v>0.003254244569689035</v>
+      </c>
+      <c r="G39">
+        <v>0.003174962243065238</v>
+      </c>
+      <c r="H39">
+        <v>1.001806988317537</v>
+      </c>
+      <c r="I39">
+        <v>0.05034160335526899</v>
+      </c>
+      <c r="J39">
+        <v>0.07900706678628922</v>
+      </c>
+      <c r="K39">
+        <v>2.834615215431635E+20</v>
+      </c>
+      <c r="L39">
+        <v>10.48940277099609</v>
+      </c>
+      <c r="M39">
+        <v>4.52207612991333</v>
+      </c>
+      <c r="N39" t="s">
+        <v>328</v>
+      </c>
+      <c r="O39" t="s">
+        <v>388</v>
+      </c>
+      <c r="P39" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.0538652855041985</v>
+      </c>
+      <c r="D40">
+        <v>0.03561006486415863</v>
+      </c>
+      <c r="E40">
+        <v>0.4663285315036774</v>
+      </c>
+      <c r="F40">
+        <v>0.003544224426150322</v>
+      </c>
+      <c r="G40">
+        <v>0.003556869458407164</v>
+      </c>
+      <c r="H40">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I40">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J40">
+        <v>0.07636260986328125</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>26.69094276428223</v>
+      </c>
+      <c r="M40">
+        <v>4.37071704864502</v>
+      </c>
+      <c r="N40" t="s">
+        <v>329</v>
+      </c>
+      <c r="O40" t="s">
+        <v>389</v>
+      </c>
+      <c r="P40" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1113508697159886</v>
+      </c>
+      <c r="D41">
+        <v>0.07255353778600693</v>
+      </c>
+      <c r="E41">
+        <v>1.003780364990234</v>
+      </c>
+      <c r="F41">
+        <v>0.003753135912120342</v>
+      </c>
+      <c r="G41">
+        <v>0.003827285254374146</v>
+      </c>
+      <c r="H41">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I41">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J41">
+        <v>0.07228029519319534</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>57.45272445678711</v>
+      </c>
+      <c r="M41">
+        <v>4.137060165405273</v>
+      </c>
+      <c r="N41" t="s">
+        <v>330</v>
+      </c>
+      <c r="O41" t="s">
+        <v>390</v>
+      </c>
+      <c r="P41" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.000180838908553695</v>
+      </c>
+      <c r="D42">
+        <v>-5.789204806205817E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001943034585565329</v>
+      </c>
+      <c r="F42">
+        <v>0.001123212627135217</v>
+      </c>
+      <c r="G42">
+        <v>0.001080207992345095</v>
+      </c>
+      <c r="H42">
+        <v>0.9998374459358941</v>
+      </c>
+      <c r="I42">
+        <v>0.04950893669356056</v>
+      </c>
+      <c r="J42">
+        <v>-0.02979465574026108</v>
+      </c>
+      <c r="K42">
+        <v>-0.1727163195610046</v>
+      </c>
+      <c r="L42">
+        <v>0.1112122088670731</v>
+      </c>
+      <c r="M42">
+        <v>-1.705337405204773</v>
+      </c>
+      <c r="N42" t="s">
+        <v>331</v>
+      </c>
+      <c r="O42" t="s">
+        <v>391</v>
+      </c>
+      <c r="P42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.000232164803366707</v>
+      </c>
+      <c r="D43">
+        <v>5.422697540780064E-06</v>
+      </c>
+      <c r="E43">
+        <v>0.002333202864974737</v>
+      </c>
+      <c r="F43">
+        <v>0.001296331058256328</v>
+      </c>
+      <c r="G43">
+        <v>0.001214966061525047</v>
+      </c>
+      <c r="H43">
+        <v>0.9999499637839324</v>
+      </c>
+      <c r="I43">
+        <v>0.04954348091882876</v>
+      </c>
+      <c r="J43">
+        <v>0.002324143191799521</v>
+      </c>
+      <c r="K43">
+        <v>0.01772916316986084</v>
+      </c>
+      <c r="L43">
+        <v>0.1335440129041672</v>
+      </c>
+      <c r="M43">
+        <v>0.1330254822969437</v>
+      </c>
+      <c r="N43" t="s">
+        <v>332</v>
+      </c>
+      <c r="O43" t="s">
+        <v>392</v>
+      </c>
+      <c r="P43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002785504111716923</v>
+      </c>
+      <c r="D44">
+        <v>6.687665154458955E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.002832143567502499</v>
+      </c>
+      <c r="F44">
+        <v>0.001407152274623513</v>
+      </c>
+      <c r="G44">
+        <v>0.001299717929214239</v>
+      </c>
+      <c r="H44">
+        <v>0.9999908888243779</v>
+      </c>
+      <c r="I44">
+        <v>0.04961787156305465</v>
+      </c>
+      <c r="J44">
+        <v>0.02361343987286091</v>
+      </c>
+      <c r="K44">
+        <v>0.244930624961853</v>
+      </c>
+      <c r="L44">
+        <v>0.1621015667915344</v>
+      </c>
+      <c r="M44">
+        <v>1.351547122001648</v>
+      </c>
+      <c r="N44" t="s">
+        <v>333</v>
+      </c>
+      <c r="O44" t="s">
+        <v>393</v>
+      </c>
+      <c r="P44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0004656881941024586</v>
+      </c>
+      <c r="D45">
+        <v>0.0004701625439338386</v>
+      </c>
+      <c r="E45">
+        <v>0.001712704193778336</v>
+      </c>
+      <c r="F45">
+        <v>0.001759056933224201</v>
+      </c>
+      <c r="G45">
+        <v>0.001638834015466273</v>
+      </c>
+      <c r="H45">
+        <v>1.00009903447419</v>
+      </c>
+      <c r="I45">
+        <v>0.04980822264358745</v>
+      </c>
+      <c r="J45">
+        <v>0.2745147347450256</v>
+      </c>
+      <c r="K45">
+        <v>3.664062976837158</v>
+      </c>
+      <c r="L45">
+        <v>0.09802893549203873</v>
+      </c>
+      <c r="M45">
+        <v>15.7122220993042</v>
+      </c>
+      <c r="N45" t="s">
+        <v>334</v>
+      </c>
+      <c r="O45" t="s">
+        <v>394</v>
+      </c>
+      <c r="P45" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0007479548839370046</v>
+      </c>
+      <c r="D46">
+        <v>0.0006911833770573139</v>
+      </c>
+      <c r="E46">
+        <v>0.002323159016668797</v>
+      </c>
+      <c r="F46">
+        <v>0.002272396814078093</v>
+      </c>
+      <c r="G46">
+        <v>0.002096368698403239</v>
+      </c>
+      <c r="H46">
+        <v>1.000328143489157</v>
+      </c>
+      <c r="I46">
+        <v>0.04989243106121275</v>
+      </c>
+      <c r="J46">
+        <v>0.2975187599658966</v>
+      </c>
+      <c r="K46">
+        <v>8.616771697998047</v>
+      </c>
+      <c r="L46">
+        <v>0.1329691410064697</v>
+      </c>
+      <c r="M46">
+        <v>17.02888870239258</v>
+      </c>
+      <c r="N46" t="s">
+        <v>335</v>
+      </c>
+      <c r="O46" t="s">
+        <v>395</v>
+      </c>
+      <c r="P46" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.001201944400914907</v>
+      </c>
+      <c r="D47">
+        <v>0.001008648774586618</v>
+      </c>
+      <c r="E47">
+        <v>0.004383958876132965</v>
+      </c>
+      <c r="F47">
+        <v>0.002696612617000937</v>
+      </c>
+      <c r="G47">
+        <v>0.002534774597734213</v>
+      </c>
+      <c r="H47">
+        <v>1.000753255511865</v>
+      </c>
+      <c r="I47">
+        <v>0.04936561876718686</v>
+      </c>
+      <c r="J47">
+        <v>0.2300771474838257</v>
+      </c>
+      <c r="K47">
+        <v>26.18338584899902</v>
+      </c>
+      <c r="L47">
+        <v>0.2509218156337738</v>
+      </c>
+      <c r="M47">
+        <v>13.168776512146</v>
+      </c>
+      <c r="N47" t="s">
+        <v>336</v>
+      </c>
+      <c r="O47" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.002370620329761253</v>
+      </c>
+      <c r="D48">
+        <v>0.001692441408522427</v>
+      </c>
+      <c r="E48">
+        <v>0.01049764454364777</v>
+      </c>
+      <c r="F48">
+        <v>0.003055745735764503</v>
+      </c>
+      <c r="G48">
+        <v>0.002970320405438542</v>
+      </c>
+      <c r="H48">
+        <v>1.001606318626973</v>
+      </c>
+      <c r="I48">
+        <v>0.0497457804845613</v>
+      </c>
+      <c r="J48">
+        <v>0.16122105717659</v>
+      </c>
+      <c r="K48">
+        <v>253.5921325683594</v>
+      </c>
+      <c r="L48">
+        <v>0.6008468866348267</v>
+      </c>
+      <c r="M48">
+        <v>9.227705001831055</v>
+      </c>
+      <c r="N48" t="s">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s">
+        <v>397</v>
+      </c>
+      <c r="P48" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.004189502901775591</v>
+      </c>
+      <c r="D49">
+        <v>0.002698598196730018</v>
+      </c>
+      <c r="E49">
+        <v>0.02057121135294437</v>
+      </c>
+      <c r="F49">
+        <v>0.003288599662482738</v>
+      </c>
+      <c r="G49">
+        <v>0.003267662134021521</v>
+      </c>
+      <c r="H49">
+        <v>1.001929055010176</v>
+      </c>
+      <c r="I49">
+        <v>0.0503188642914687</v>
+      </c>
+      <c r="J49">
+        <v>0.1311832368373871</v>
+      </c>
+      <c r="K49">
+        <v>6825.1259765625</v>
+      </c>
+      <c r="L49">
+        <v>1.177421092987061</v>
+      </c>
+      <c r="M49">
+        <v>7.508449554443359</v>
+      </c>
+      <c r="N49" t="s">
+        <v>338</v>
+      </c>
+      <c r="O49" t="s">
+        <v>398</v>
+      </c>
+      <c r="P49" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.009647124129132727</v>
+      </c>
+      <c r="D50">
+        <v>0.005599686875939369</v>
+      </c>
+      <c r="E50">
+        <v>0.05341349169611931</v>
+      </c>
+      <c r="F50">
+        <v>0.003594326321035624</v>
+      </c>
+      <c r="G50">
+        <v>0.003602892160415649</v>
+      </c>
+      <c r="H50">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I50">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J50">
+        <v>0.1048365607857704</v>
+      </c>
+      <c r="K50">
+        <v>88063352</v>
+      </c>
+      <c r="L50">
+        <v>3.057193279266357</v>
+      </c>
+      <c r="M50">
+        <v>6.000462055206299</v>
+      </c>
+      <c r="N50" t="s">
+        <v>339</v>
+      </c>
+      <c r="O50" t="s">
+        <v>399</v>
+      </c>
+      <c r="P50" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01810795950611202</v>
+      </c>
+      <c r="D51">
+        <v>0.01015379372984171</v>
+      </c>
+      <c r="E51">
+        <v>0.1023937612771988</v>
+      </c>
+      <c r="F51">
+        <v>0.003811323316767812</v>
+      </c>
+      <c r="G51">
+        <v>0.003928344696760178</v>
+      </c>
+      <c r="H51">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I51">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J51">
+        <v>0.09916418045759201</v>
+      </c>
+      <c r="K51">
+        <v>236273281269760</v>
+      </c>
+      <c r="L51">
+        <v>5.860645294189453</v>
+      </c>
+      <c r="M51">
+        <v>5.675796031951904</v>
+      </c>
+      <c r="N51" t="s">
+        <v>340</v>
+      </c>
+      <c r="O51" t="s">
+        <v>400</v>
+      </c>
+      <c r="P51" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001935009464396488</v>
+      </c>
+      <c r="D52">
+        <v>0.0002621407620608807</v>
+      </c>
+      <c r="E52">
+        <v>0.0005237080622464418</v>
+      </c>
+      <c r="F52">
+        <v>0.001247630687430501</v>
+      </c>
+      <c r="G52">
+        <v>0.001241872319951653</v>
+      </c>
+      <c r="H52">
+        <v>0.9993216257232495</v>
+      </c>
+      <c r="I52">
+        <v>0.05006021387802654</v>
+      </c>
+      <c r="J52">
+        <v>0.5005475282669067</v>
+      </c>
+      <c r="K52">
+        <v>1.360001087188721</v>
+      </c>
+      <c r="L52">
+        <v>0.02997513860464096</v>
+      </c>
+      <c r="M52">
+        <v>28.64951324462891</v>
+      </c>
+      <c r="N52" t="s">
+        <v>341</v>
+      </c>
+      <c r="O52" t="s">
+        <v>401</v>
+      </c>
+      <c r="P52" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0002373742871040713</v>
+      </c>
+      <c r="D53">
+        <v>0.0003165342495776713</v>
+      </c>
+      <c r="E53">
+        <v>0.0005897700903005898</v>
+      </c>
+      <c r="F53">
+        <v>0.001352674793452024</v>
+      </c>
+      <c r="G53">
+        <v>0.001353070954792202</v>
+      </c>
+      <c r="H53">
+        <v>0.9993011363762473</v>
+      </c>
+      <c r="I53">
+        <v>0.05015470085608741</v>
+      </c>
+      <c r="J53">
+        <v>0.536707878112793</v>
+      </c>
+      <c r="K53">
+        <v>1.819873809814453</v>
+      </c>
+      <c r="L53">
+        <v>0.03375628963112831</v>
+      </c>
+      <c r="M53">
+        <v>30.71920013427734</v>
+      </c>
+      <c r="N53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" t="s">
+        <v>402</v>
+      </c>
+      <c r="P53" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.000273169334097974</v>
+      </c>
+      <c r="D54">
+        <v>0.0003602399665396661</v>
+      </c>
+      <c r="E54">
+        <v>0.0006337244412861764</v>
+      </c>
+      <c r="F54">
+        <v>0.001423295121639967</v>
+      </c>
+      <c r="G54">
+        <v>0.001426620641723275</v>
+      </c>
+      <c r="H54">
+        <v>0.9993317107310935</v>
+      </c>
+      <c r="I54">
+        <v>0.05029025702996403</v>
+      </c>
+      <c r="J54">
+        <v>0.5684489011764526</v>
+      </c>
+      <c r="K54">
+        <v>2.254270076751709</v>
+      </c>
+      <c r="L54">
+        <v>0.0362720750272274</v>
+      </c>
+      <c r="M54">
+        <v>32.53594207763672</v>
+      </c>
+      <c r="N54" t="s">
+        <v>343</v>
+      </c>
+      <c r="O54" t="s">
+        <v>403</v>
+      </c>
+      <c r="P54" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0003918104636698624</v>
+      </c>
+      <c r="D55">
+        <v>0.0005080005503259599</v>
+      </c>
+      <c r="E55">
+        <v>0.0007544612162746489</v>
+      </c>
+      <c r="F55">
+        <v>0.001777717960067093</v>
+      </c>
+      <c r="G55">
+        <v>0.001780090504325926</v>
+      </c>
+      <c r="H55">
+        <v>0.9995893426341524</v>
+      </c>
+      <c r="I55">
+        <v>0.05035595365797364</v>
+      </c>
+      <c r="J55">
+        <v>0.6733289361000061</v>
+      </c>
+      <c r="K55">
+        <v>4.278406620025635</v>
+      </c>
+      <c r="L55">
+        <v>0.0431826077401638</v>
+      </c>
+      <c r="M55">
+        <v>38.53889083862305</v>
+      </c>
+      <c r="N55" t="s">
+        <v>344</v>
+      </c>
+      <c r="O55" t="s">
+        <v>404</v>
+      </c>
+      <c r="P55" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0005137193355180842</v>
+      </c>
+      <c r="D56">
+        <v>0.0006478392169810832</v>
+      </c>
+      <c r="E56">
+        <v>0.0009144852519966662</v>
+      </c>
+      <c r="F56">
+        <v>0.002277216408401728</v>
+      </c>
+      <c r="G56">
+        <v>0.002336052479222417</v>
+      </c>
+      <c r="H56">
+        <v>1.000137697823166</v>
+      </c>
+      <c r="I56">
+        <v>0.05025895802576521</v>
+      </c>
+      <c r="J56">
+        <v>0.7084195613861084</v>
+      </c>
+      <c r="K56">
+        <v>7.343235015869141</v>
+      </c>
+      <c r="L56">
+        <v>0.05234180018305779</v>
+      </c>
+      <c r="M56">
+        <v>40.5473518371582</v>
+      </c>
+      <c r="N56" t="s">
+        <v>345</v>
+      </c>
+      <c r="O56" t="s">
+        <v>405</v>
+      </c>
+      <c r="P56" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.000626169647687993</v>
+      </c>
+      <c r="D57">
+        <v>0.0007568458677269518</v>
+      </c>
+      <c r="E57">
+        <v>0.001079457928426564</v>
+      </c>
+      <c r="F57">
+        <v>0.002622055355459452</v>
+      </c>
+      <c r="G57">
+        <v>0.002685519400984049</v>
+      </c>
+      <c r="H57">
+        <v>1.000894094451344</v>
+      </c>
+      <c r="I57">
+        <v>0.04926272111146764</v>
+      </c>
+      <c r="J57">
+        <v>0.7011350989341736</v>
+      </c>
+      <c r="K57">
+        <v>10.9237813949585</v>
+      </c>
+      <c r="L57">
+        <v>0.06178423389792442</v>
+      </c>
+      <c r="M57">
+        <v>40.13041305541992</v>
+      </c>
+      <c r="N57" t="s">
+        <v>346</v>
+      </c>
+      <c r="O57" t="s">
+        <v>406</v>
+      </c>
+      <c r="P57" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0007547293976818992</v>
+      </c>
+      <c r="D58">
+        <v>0.0009015514515340328</v>
+      </c>
+      <c r="E58">
+        <v>0.001426191534847021</v>
+      </c>
+      <c r="F58">
+        <v>0.003032217733561993</v>
+      </c>
+      <c r="G58">
+        <v>0.003130324417725205</v>
+      </c>
+      <c r="H58">
+        <v>1.00141724661613</v>
+      </c>
+      <c r="I58">
+        <v>0.04959998637033777</v>
+      </c>
+      <c r="J58">
+        <v>0.6321390867233276</v>
+      </c>
+      <c r="K58">
+        <v>18.14889335632324</v>
+      </c>
+      <c r="L58">
+        <v>0.08162999898195267</v>
+      </c>
+      <c r="M58">
+        <v>36.18133544921875</v>
+      </c>
+      <c r="N58" t="s">
+        <v>347</v>
+      </c>
+      <c r="O58" t="s">
+        <v>407</v>
+      </c>
+      <c r="P58" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0008422022797184778</v>
+      </c>
+      <c r="D59">
+        <v>0.001008623279631138</v>
+      </c>
+      <c r="E59">
+        <v>0.00198879768140614</v>
+      </c>
+      <c r="F59">
+        <v>0.00328511418774724</v>
+      </c>
+      <c r="G59">
+        <v>0.003431895980611444</v>
+      </c>
+      <c r="H59">
+        <v>1.001700288897721</v>
+      </c>
+      <c r="I59">
+        <v>0.05021852846131143</v>
+      </c>
+      <c r="J59">
+        <v>0.507152259349823</v>
+      </c>
+      <c r="K59">
+        <v>26.18338584899902</v>
+      </c>
+      <c r="L59">
+        <v>0.1138315200805664</v>
+      </c>
+      <c r="M59">
+        <v>29.02754402160645</v>
+      </c>
+      <c r="N59" t="s">
+        <v>348</v>
+      </c>
+      <c r="O59" t="s">
+        <v>408</v>
+      </c>
+      <c r="P59" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0009511160556999905</v>
+      </c>
+      <c r="D60">
+        <v>0.001187341404147446</v>
+      </c>
+      <c r="E60">
+        <v>0.003189242677763104</v>
+      </c>
+      <c r="F60">
+        <v>0.003508836030960083</v>
+      </c>
+      <c r="G60">
+        <v>0.003718019463121891</v>
+      </c>
+      <c r="H60">
+        <v>1.00247162568154</v>
+      </c>
+      <c r="I60">
+        <v>0.05581479831805958</v>
+      </c>
+      <c r="J60">
+        <v>0.3722957074642181</v>
+      </c>
+      <c r="K60">
+        <v>47.78231430053711</v>
+      </c>
+      <c r="L60">
+        <v>0.1825406104326248</v>
+      </c>
+      <c r="M60">
+        <v>21.30884742736816</v>
+      </c>
+      <c r="N60" t="s">
+        <v>349</v>
+      </c>
+      <c r="O60" t="s">
+        <v>409</v>
+      </c>
+      <c r="P60" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.001029130735698351</v>
+      </c>
+      <c r="D61">
+        <v>0.001379755674861372</v>
+      </c>
+      <c r="E61">
+        <v>0.004413841292262077</v>
+      </c>
+      <c r="F61">
+        <v>0.003644472919404507</v>
+      </c>
+      <c r="G61">
+        <v>0.003955302760004997</v>
+      </c>
+      <c r="H61">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I61">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J61">
+        <v>0.3125974833965302</v>
+      </c>
+      <c r="K61">
+        <v>90.54902648925781</v>
+      </c>
+      <c r="L61">
+        <v>0.2526321709156036</v>
+      </c>
+      <c r="M61">
+        <v>17.89193916320801</v>
+      </c>
+      <c r="N61" t="s">
+        <v>350</v>
+      </c>
+      <c r="O61" t="s">
+        <v>410</v>
+      </c>
+      <c r="P61" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/ffn_discrete/performance.xlsx
+++ b/scripts/ffn_discrete/performance.xlsx
@@ -8919,12 +8919,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0001101214365917258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.0001483105006627738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0008294894942082465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.0002506313321646303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0002438490046188235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-4.112493843422271E-05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0003788509930018336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0002319871709914878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.001000840100459754</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0003813251387327909</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0002563812886364758</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.00158561032731086</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.0003684938128571957</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>6.786952872062102E-05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0003429174248594791</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-1.040245570038678E-05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-0.0006375701632350683</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.0009317382937297225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0002403433027211577</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0005038062226958573</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.0001854230213211849</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.0007510652067139745</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.0008527507889084518</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0009143759962171316</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.001806663349270821</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.001258479780517519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.0001607728627277538</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0001238973345607519</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.0005200828891247511</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.0004847916716244072</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0002526953758206218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0006585164810530841</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>1.401449571858393E-05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.00014482245023828</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0006903116591274738</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.0002915882505476475</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.0003101101028732955</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0004240418784320354</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.0004309374198783189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0006786676240153611</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.0002078212128253654</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>9.013383532874286E-05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-0.000418977637309581</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.001301123527809978</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.001091379905119538</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>2.400525045231916E-05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>-3.540706529747695E-05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.000329941714880988</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0003350194601807743</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0002868590236175805</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.001099194982089102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>-3.556585215847008E-05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-7.724480383330956E-05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.0008490517502650619</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>-9.589025285094976E-05</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0007291180081665516</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>-0.0003106628137174994</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.0003530561807565391</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.000392378744436428</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0004833588318433613</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0001055267930496484</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>-0.0002784807002171874</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0005048371385782957</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.001771091599948704</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0005312948487699032</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0007135375053621829</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0002541143330745399</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0003733480989467353</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.0005825140397064388</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.0008016007486730814</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>-0.0001377982116537169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.0006124202627688646</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0007407845114357769</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.0009193537989631295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001268032006919384</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.0001813189737731591</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.002159955445677042</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0005957269459031522</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0002247435477329418</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>0.0001937689812621102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>0.0002468747261445969</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0003195913450326771</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.0002843098773155361</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>2.428175503155217E-05</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>-8.783446901361458E-06</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>9.732555918162689E-05</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0006285788840614259</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>-3.191130963386968E-05</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0006769665633328259</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0003351526102051139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.0001188657988677733</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>3.331444167997688E-05</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0007483613444492221</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.001167717389762402</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>2.065596345346421E-05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0004328280338086188</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.000253104604780674</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0002955215750262141</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0001564580452395603</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>6.102617044234648E-05</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.0002413351176073775</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-7.48740931157954E-05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>-0.0006011779187247157</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.0003585304657462984</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0002405265404377133</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.0011380217038095</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001668552868068218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>-0.00016327018965967</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0001236943498952314</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001553201000206172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.000456226640380919</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>-0.0002746515674516559</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.0004912688746117055</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0001876925089163706</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>2.982277010232792E-06</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>0.002824429888278246</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.0003079817106481642</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.0001522871752968058</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>0.0001169502211268991</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>0.0001644659350859001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0006566584925167263</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>-0.0001740985317155719</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0007042778306640685</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0007157755899243057</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>-0.0002173643879359588</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.001805531443096697</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0004088512214366347</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0004965721163898706</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>0.0002820213267114013</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001060548820532858</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>0.0002586293267086148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-3.384737647138536E-05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>0.0002526735188439488</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0002259383763885126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0003610834246501327</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.001063297037035227</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0002615163684822619</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>-5.009038068237714E-05</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0008159572025761008</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>0.0002273618447361514</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0005384669057093561</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.002975084818899632</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>-0.0004254663072060794</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.0006905835471116006</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>-5.43149872100912E-06</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>0.0001997917570406571</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.0007620195392519236</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.0006822822033427656</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.0001968277792911977</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0004274162638466805</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0002829294244293123</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.000518132874276489</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>0.0004981796373613179</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>0.0004476425820030272</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.001864461926743388</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0004251058562658727</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0004386042128317058</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.00112549785990268</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0004683577280957252</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0004557905776891857</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0002682930207811296</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0001660613052081317</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0006032245000824332</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.0004960685619153082</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0002041276602540165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.0007777626160532236</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>0.000109163906017784</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.001556108938530087</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0004748556821141392</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>5.212462929193862E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>0.0002644240448717028</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0001374990242766216</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.0004912924487143755</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>0.0003449035284575075</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0002980845456477255</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0003170290437992662</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0001812126283766702</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.0003786535817198455</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0004270207427907735</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0004477344918996096</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>0.001643157913349569</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-1.402202906319872E-05</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>0.0003242452221456915</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0002581496955826879</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0002837009378708899</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.0002569531498011202</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.0003406719770282507</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.002096905838698149</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.00049977918388322</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0005651069222949445</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.0007706775213591754</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0002566555922385305</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>0.0007519847713410854</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>0.002719481475651264</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.0009728508302941918</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>0.0001440345658920705</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0009603719809092581</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0001466129615437239</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>9.545868670102209E-05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0005513983778655529</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>8.430735033471137E-05</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>-0.0003950622631236911</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.001745934481732547</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0003050575905945152</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>4.080987127963454E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0004182765551377088</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.0006878825952298939</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>0.0005895451758988202</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.00120435981079936</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0002788886486086994</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.0003580649790819734</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0005082728457637131</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.000184771852218546</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0002104890736518428</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0002508369216229767</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0004695621028076857</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0004227167810313404</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>0.000404508231440559</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0004255332169122994</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.001475189113989472</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.001419358537532389</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>0.0005447004223242402</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.0008610020740889013</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0004321529122535139</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.001005073310807347</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.0006598405889235437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-7.894859299995005E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0004847699601668864</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.001663602190092206</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.001030409126542509</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002179828006774187</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>0.0004384664352983236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0006781919510103762</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0006239709910005331</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>0.000153593355207704</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0007749561336822808</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.0004117371572647244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>-0.000595967925619334</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-0.000256086204899475</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.002257900079712272</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>1.158934628620045E-05</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>-0.0001000529300654307</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0004822328919544816</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>-0.0001196197190438397</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>0.0001118762447731569</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.003025263082236052</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0004973557661287487</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-7.381279374385485E-07</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0006899501895532012</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.0001129196753026918</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0005627819336950779</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0004177314403932542</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>3.80672026949469E-05</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>0.001317002926953137</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>0.0002909995091613382</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0002252838748972863</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0001965679402928799</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.0001579149829922244</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001450513722375035</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0002606583584565669</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.000382426573196426</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>-4.522076778812334E-05</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>0.0001320043520536274</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>0.0001520454097772017</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0004764745535794646</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>5.610339576378465E-05</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>6.63812852508272E-06</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.0008836933993734419</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>0.0001048652629833668</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0002216014690930024</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0002355073811486363</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.000901299063116312</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0004396801814436913</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0004674414813052863</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>0.0001114706028602086</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0001902148796943948</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>0.0001089704819605686</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0002495947992429137</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.0001612654014024884</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0005747310933656991</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0001967577991308644</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0007119562360458076</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>4.661635466618463E-05</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-1.224857169290772E-05</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.001363614108413458</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.000622085586655885</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.0007599134696647525</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0002513330546207726</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>-2.165088517358527E-06</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>-0.0002757304173428565</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.0008600974106229842</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0004175008798483759</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>-0.0002925245498772711</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0007272535585798323</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0003411018988117576</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0004104548133909702</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0005472661578096449</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001214918913319707</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>-0.0001913097949000075</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0005136917461641133</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>-0.0002566977636888623</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.00040029501542449</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0003601748030632734</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>-0.0001985372655326501</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0003264431725256145</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002366562548559159</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0003032220993191004</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0009083680924959481</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0003569318796508014</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>-1.132955094362842E-05</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0008266277727670968</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>0.0001180002655019052</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001251932349987328</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0007752067176625133</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0003349054895807058</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.001005848869681358</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.0001497482444392517</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>-0.0001886115496745333</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>-2.590709482319653E-05</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.001079393434338272</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0002933703945018351</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-0.000348141067661345</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0007901637582108378</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.0008575576939620078</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>0.0008600855944678187</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.0006568913231603801</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.0002338055346626788</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>0.0001116547937272117</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>-2.588524512248114E-05</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>8.710219117347151E-05</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001504087937064469</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001015574671328068</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.001246173167601228</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.0003132075944449753</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0005367152043618262</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001939898356795311</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.0003137729945592582</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>-0.0001667386677581817</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.001136096543632448</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.0005716752493754029</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.001030358020216227</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.0002425555576337501</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>-0.000252220401307568</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.001148617593571544</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>6.922140892129391E-05</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0004128417931497097</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0001516658085165545</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0005282927886582911</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0005234596319496632</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0004822809714823961</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.0009733732440508902</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0005988788907416165</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0007535903714597225</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.0005910492618568242</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.001169150345958769</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0005833428003825247</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>2.366000080655795E-05</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>-0.0001277605624636635</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005890856846235693</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.0003488287911750376</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>3.062207906623371E-05</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.00220179557800293</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.0001338386064162478</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001461465726606548</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>-1.73968273884384E-05</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0008818482747301459</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>4.309248834033497E-05</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.001187843736261129</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-0.0002334964810870588</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>7.025464583421126E-05</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0004054070450365543</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0002966802858281881</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0009487567585892975</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>-0.0001145362693932839</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.0008861874230206013</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.002877177204936743</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>-1.646486998652108E-05</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>4.738379720947705E-05</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.0003643196541815996</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0003109697136096656</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0009481329470872879</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>1.545783925394062E-05</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0006169946282170713</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>0.0001225107698701322</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>-0.0001694717793725431</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001427665818482637</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.001663301605731249</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001690075499936938</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.001000385032966733</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.0008341218926943839</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0005279442993924022</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.0009936111746355891</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001326651661656797</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0001761395833455026</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>0.0002624588669277728</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0001796078868210316</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0001510188012616709</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>-0.0002590894582681358</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-0.000368517154129222</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0002943541039712727</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>0.0001610469771549106</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>4.563766924547963E-05</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.0007818666053935885</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.000810125085990876</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0002407482825219631</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.002494808286428452</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>-0.0008587779011577368</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-0.0001796131691662595</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.0004400874313432723</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>-2.185133962484542E-05</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>3.245518018957227E-05</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0001012933425954543</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0008104070439003408</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>0.001398527645505965</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.00025736223324202</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0002622180327307433</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0002292048593517393</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0008802824886515737</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0006096066208556294</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0005485035944730043</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001628470490686595</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-0.0002726272505242378</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.001003091339953244</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0003687191929202527</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001600906834937632</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0005712526035495102</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001282710116356611</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.001057324931025505</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.002054192824289203</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>-0.0004348043876234442</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0001100416629924439</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0005156787228770554</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001315398258157074</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0007885638624429703</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0002829707518685609</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0003342735290061682</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.001068176468834281</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>-5.492451600730419E-05</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.001546235522255301</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.002428478328511119</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>2.422096440568566E-05</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0004581207176670432</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0006064650369808078</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0008577931439504027</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>-0.000210445505217649</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003399419074412435</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0004625184810720384</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.0004309511568862945</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.0002425714628770947</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>0.0002783846284728497</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-0.0001347193756373599</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.000448090402642265</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001219261204823852</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.000720194133464247</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.0002527635951992124</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0006341959815472364</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0008883075206540525</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0005130569916218519</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0002962900034617633</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001198629732243717</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0002085612359223887</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.0006869648350402713</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0001710675715003163</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.000389507447835058</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001047450117766857</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0007532340823672712</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001719822292216122</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0003045732446480542</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001372872502543032</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0008395009790547192</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.0003185693349223584</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>-0.0001781315222615376</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.000312165153445676</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0006017915438860655</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0002147050254279748</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>-1.98670804820722E-05</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.0007364812772721052</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.0005414543556980789</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.00426640035584569</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.001162699423730373</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>-0.0005251527763903141</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0009199758642353117</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>0.0003717896470334381</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.000548511219676584</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-5.864350168849342E-05</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0002605400804895908</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>0.0001742561144055799</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.0009213103330694139</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0004524827818386257</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.0003066858334932476</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0004593865014612675</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.0004830360412597656</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0002473187341820449</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0009394156513735652</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0001919909554999322</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.000880911888089031</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0001822680642362684</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0001092372112907469</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.0001063598319888115</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.000418791314586997</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0005911581683903933</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0006694290786981583</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001495027216151357</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.0003547157684806734</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0002380274963798001</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001733874320052564</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.000703008146956563</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.0005450230091810226</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.0003999551699962467</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>-5.208215225138701E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0004468097467906773</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005439785891212523</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0001144523339462467</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>-9.886951011139899E-05</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>0.0001197725505335256</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-0.0002841403475031257</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001216097618453205</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.001124404021538794</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0003448341740295291</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>6.117645534686744E-05</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0006174672744236887</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0002513422805350274</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0008870494784787297</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001807264401577413</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.0003578384930733591</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001554510672576725</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>0.0001573774497956038</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>0.000383217673515901</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0002984186576213688</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0008074598154053092</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0004770338709931821</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>-3.302042387076654E-06</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0007412056438624859</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0007258101250045002</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>0.0005067932070232928</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001683333073742688</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>0.0002751481952145696</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.0005031739128753543</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>-3.964826464653015E-05</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>3.347198071423918E-05</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0005261928890831769</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0003440106811467558</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>0.0001194783762912266</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0002854311605915427</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0007781149470247328</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0003951549879275262</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.001009275089018047</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0006852006772533059</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.0003867183404508978</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0005229723174124956</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001689802506007254</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001210109796375036</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0003398088156245649</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0007507153204642236</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0009260199149139225</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0008064218563959002</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.0009544874774292111</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001419294159859419</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.0007810167735442519</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.001734401099383831</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.0003001399454660714</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>0.0001574005727889016</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0008884833077900112</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.002161978743970394</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001431239303201437</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0004403961065690964</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0003383785951882601</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.0005047316080890596</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.0007748560747131705</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.0002206733333878219</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0007950995350256562</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.0004919713828712702</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.0008769692503847182</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.002455285284668207</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0004652960051316768</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>-3.74348383047618E-05</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.002170059597119689</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.001162993838079274</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.0004567445430438966</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.001021216390654445</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001665836665779352</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0002965603198390454</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0001106378695112653</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0005363442469388247</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0005570969660766423</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>0.0001311575470026582</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0008590695215389132</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0003208554117009044</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>0.0003253203176427633</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>-0.0001078972927643918</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0009698756039142609</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001773843076080084</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>0.0001387525117024779</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0007531856535933912</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0006959489546716213</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.001092644175514579</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>0.0003123627975583076</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-2.520712223486044E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>-0.0001423812209395692</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001761235180310905</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.00337626994587481</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.00218479847535491</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.006291292607784271</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.001260988414287567</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>0.0001701524161035195</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001057894318364561</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.002656080527231097</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.0003972443228121847</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0003478919097688049</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0004607306909747422</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0001916205219458789</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0004753934917971492</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>5.325693928170949E-05</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0007598662050440907</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>-3.790729533648118E-05</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>0.001149782561697066</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0001893789594760165</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-4.208691098028794E-05</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0003480199666228145</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.002180177252739668</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.000536937324795872</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.0008415800984948874</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>-0.0006921214517205954</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.001193886157125235</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>0.0005287912208586931</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.000312837160890922</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0003522869083099067</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0007146833813749254</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>0.001700888969935477</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0006938321166671813</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001367481192573905</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.0004055432800669223</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.001256971387192607</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.001031495863571763</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>0.0002872127515729517</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0006223749369382858</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.000710650288965553</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0005739908665418625</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.00131361570674926</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.001474180724471807</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0003705326234921813</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>0.002314128912985325</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.001274098991416395</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001202535117045045</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0009387771715410054</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>-5.545568637899123E-05</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>0.001907107653096318</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>-0.0002558592241257429</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001622796175070107</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.000335828895913437</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.0009629764244891703</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0003758873790502548</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.0002531014033593237</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.0007676674867980182</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.00178248411975801</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>-0.0001912269508466125</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0007704102317802608</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>-0.0001151201577158645</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>0.001100059365853667</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003054238157346845</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.00110123585909605</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>-0.000251150835538283</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0008679092861711979</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.002117933239787817</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.001259060576558113</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>-4.53934189863503E-05</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.002527067437767982</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.003700398141518235</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0006570384721271694</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.000184067539521493</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.0005397434579208493</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>-9.636796312406659E-05</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0003585629165172577</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0004161249671597034</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0005164301255717874</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.001042869640514255</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.000541484565474093</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0005477790837176144</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>3.38580139214173E-05</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>-8.624621841590852E-05</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.004535280633717775</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>-0.0002995441318489611</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.001014045672491193</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>-6.936990394024178E-05</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0009494568803347647</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0007509060669690371</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>-0.0002806840930134058</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0008796152542345226</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>-0.0003555580624379218</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001694489852525294</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>0.00067477225093171</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>0.0002388639259152114</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.0004868488758802414</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001454677199944854</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>0.0002962854341603816</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>-0.0003221725055482239</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0002856439677998424</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>1.011505628412124E-05</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0006987967062741518</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>0.0002227305085398257</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0001030925195664167</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.0009937538998201489</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>-0.0003011259832419455</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0004295533581171185</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0006966031505726278</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0004469135601539165</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>0.00447766249999404</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.0006635238532908261</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.001389921526424587</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>-1.901347059174441E-05</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0006662224186584353</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.0007785447523929179</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>-0.0004346164641901851</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>3.611020292737521E-05</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0008411482558585703</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.001277232193388045</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0005052002961747348</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.0003508852969389409</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>-0.0008864175179041922</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>0.001025430392473936</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>0.0002385801635682583</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0002750419662334025</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0003936245630029589</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.000497611181344837</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>-0.0005205468623898923</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.000629135116469115</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0006608497351408005</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.00046930494136177</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>-8.21804569568485E-05</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.0007101098308339715</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0003997126477770507</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.000339105783496052</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005325774196535349</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.001325702643953264</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.0005380483926273882</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0003895892004948109</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.000296671554679051</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0003915955312550068</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>-0.0001456175959901884</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>0.0002891003678087145</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>0.0002288988616783172</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.0005187835195101798</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>6.143943028291687E-05</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.001046780147589743</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>-0.001018041279166937</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>-0.0004037274338770658</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.001936900662258267</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001846566679887474</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0005544553278014064</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0004924691165797412</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>-0.0002290406991960481</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0002621070307213813</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.000481752707855776</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0008609650540165603</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0003299379604868591</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0007985748816281557</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.000362048129318282</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.001136852195486426</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.001344667514786124</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0007534103933721781</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>0.0002906851004809141</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>0.0001123658585129306</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0004849737451877445</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-3.040513911400922E-05</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0007099826470948756</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.002029585652053356</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.00117199553642422</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>2.527332071622368E-05</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0003775545337703079</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0004961021477356553</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>-0.0002135411777999252</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>0.0003475595149211586</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0005787038244307041</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001539702643640339</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.002116665476933122</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-4.558995715342462E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002094383380608633</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>0.0001501054066466168</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.001313871354795992</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0007619291427545249</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0006247073761187494</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.001253089983947575</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0004388741217553616</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>0.0002435429196339101</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>0.0002621650055516511</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0002211794344475493</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0005445735296234488</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>9.748658339958638E-05</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>-0.0001157116785179824</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0009226006222888827</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0003941359464079142</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.0002891277254093438</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>0.0001624896394787356</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0007061908836476505</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>9.457900887355208E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>0.0002516281383577734</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>-0.0001829961984185502</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>-9.346415754407644E-05</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-4.05231949116569E-05</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0005716862506233156</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>3.11389612761559E-06</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-0.0001755435660015792</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.0001922038063639775</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.001123442430980504</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.001339796697720885</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.0004593676421791315</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.001422309200279415</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0007364023476839066</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0003724062698893249</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.000359617086360231</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001280529424548149</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0007933300803415477</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0005503434804268181</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001203268649987876</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0009224311215803027</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0006568145472556353</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>0.0002718557952903211</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.002826505340635777</v>
       </c>
     </row>
   </sheetData>
@@ -8934,12 +15478,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.005759000778198242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.007228732109069824</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.003415465354919434</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.004963874816894531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.00496673583984375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.007500410079956055</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.003113627433776855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.003096103668212891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.007586121559143066</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.006188154220581055</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.005402565002441406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.007010936737060547</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.007166624069213867</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.004979372024536133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.01014089584350586</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.004003763198852539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.004669427871704102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.008594036102294922</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.006668806076049805</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.005209565162658691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.003481030464172363</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.004802227020263672</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.002338886260986328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.003281235694885254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.00354301929473877</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.007791638374328613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.005889058113098145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.004474401473999023</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.007235169410705566</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.008905768394470215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.004279851913452148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.005315184593200684</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.01046597957611084</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.008411526679992676</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.001634120941162109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.008060932159423828</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.009677886962890625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.00604248046875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.007220745086669922</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.004489541053771973</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008367180824279785</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.006152510643005371</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.01154196262359619</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.004597783088684082</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01179778575897217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.005533337593078613</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0201798677444458</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.006975412368774414</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.01002955436706543</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.01309096813201904</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.006418943405151367</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.005779266357421875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.006139278411865234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.00664973258972168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.007023930549621582</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.004925131797790527</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.009356141090393066</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.006426215171813965</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.006822705268859863</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.007682323455810547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.005350708961486816</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.002948641777038574</v>
       </c>
     </row>
   </sheetData>
@@ -8949,12 +15989,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.02660930156707764</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.02777838706970215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.03517639636993408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02948057651519775</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.01756691932678223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03476381301879883</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.03044700622558594</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.03599095344543457</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.04316329956054688</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0569995641708374</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.03242313861846924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03570687770843506</v>
       </c>
     </row>
   </sheetData>
